--- a/rf_comparison.xlsx
+++ b/rf_comparison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\Skripsi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C2048B-3354-4D22-B86C-31A455F580B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D210C8B6-D8F6-4221-9268-096F51CDB486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="988">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="987">
   <si>
     <t>Original</t>
   </si>
@@ -44,13 +44,13 @@
     <t>WD lagi coy di MAHASLOT royal bro 20jt dikasih nya hahah mantap #MAHASLOT</t>
   </si>
   <si>
-    <t>wd gila gila mahaslot royal bro juta kasih hahaha mantap mahaslot</t>
+    <t>wd keren mahaslot royal gan kasih juta hahaha mantap mahaslot</t>
   </si>
   <si>
     <t>Gacor parah ey mantap #MAHASLOT</t>
   </si>
   <si>
-    <t>serius gacor ey mantap mahaslot</t>
+    <t>jelek banget mantap mahaslot</t>
   </si>
   <si>
     <t>🤑Udah Siap Buat Klaim 𝗙𝗥𝗘𝗘𝗕𝗘𝗧 𝗣𝗘𝗣𝗘𝟴𝟴𝟵 ?
@@ -66,19 +66,26 @@
 • Klik APPLY</t>
   </si>
   <si>
-    <t>wajah materialistis laku klaim freebet pepe klaim kilau grup telegram {LINK} kilau taut daftar {LINK} masuk klik promosi klik bonus masuk kode klik laku</t>
+    <t>wajah materialistis laku klaim freebet pepe klaim kilau grup telegram {LINK} kilau taut daftar {LINK} masuk klik promo klik bonus masuk kode klik terap</t>
+  </si>
+  <si>
+    <t>Kkwin🔥baru .
+https://bit.ly/Kkwinbarurilis</t>
+  </si>
+  <si>
+    <t>kkwin api {LINK}</t>
   </si>
   <si>
     <t>𝐒𝐇𝐈𝐎𝐊𝐀𝐌𝐁𝐈𝐍𝐆𝟓  Link paling ajaib kasih scatter Tanpa hitungan modal besar langsung di kasih JP</t>
   </si>
   <si>
-    <t>shiokambing taut ajaib pencar hitung modal jp langsung</t>
+    <t>shiokambing link ajaib scatter hitung modal langsung jp</t>
   </si>
   <si>
     <t>Ku kira isi nya ga sesuai ekspetasi ternyata,,gilak bener bray Cobain aja kalau ga caya tqBONBON777</t>
   </si>
   <si>
-    <t>isi sesuai ekspektasi nyata gila gan coba percaya tqbonbon</t>
+    <t>isi sesuai ekspektasi nyata gila banget gan coba gak percaya tqbonbon</t>
   </si>
   <si>
     <t>🔥 SPECIAL NEW PROVIDER GAME PANASNYA GGSOFT #PANEN138
@@ -87,13 +94,13 @@
 LINK DAFTAR :https://heylink .me/maricuanbersamapanen138</t>
   </si>
   <si>
-    <t>api khusus sedia game hot ggsoft panen api modal ribu hasil juta tabrak nikmat utama main panen uang sayap link daftar {LINK} me maricuanbersamapanen</t>
+    <t>api sedia game panas khusus ggsoft panen api modal rb hasil juta tabrak nikmat uang main panen uang sayap taut daftar {LINK} me maricuanbersamapanen</t>
   </si>
   <si>
     <t>Info aja lur selagi masih bagus'nya baru dikash jepe besar gacor linkSAKAU007</t>
   </si>
   <si>
-    <t>info mumpung bagus kasih link jepe gacor sakau</t>
+    <t>beritahu mumpung bagus masuk jepe gacor linkakau</t>
   </si>
   <si>
     <t>💱List apk Slot WD Tampa DP
@@ -114,7 +121,7 @@
 https://bigwinner6.com?chn=bnRfNzc3d2luX2Jn&amp;id=ODYyNDgwNDk5</t>
   </si>
   <si>
-    <t>kurs daftar apk slot wd tampa dp tanda merah bonus depo k k anggota putar super tanda panah kanan taut apk tanda panah {LINK} rr tanda panah kanan taut apk tanda panah {LINK} slot tanda panah kanan taut apk tanda panah {LINK} sp tanda panah kanan taut apk tanda panah {LINK} menang tanda panah kanan taut apk tanda panah {LINK}</t>
+    <t>kurs daftar apk slot wd dp tanda merah deposit rb bonus rb anggota putar super tanda panah kanan taut apk tanda panah {LINK} rr tanda panah kanan taut apk tanda panah {LINK} slot tanda panah kanan taut apk tanda panah {LINK} sp tanda panah kanan taut apk tanda panah {LINK} menang tanda panah kanan taut apk tanda panah {LINK}</t>
   </si>
   <si>
     <t>Puput Melani</t>
@@ -129,7 +136,7 @@
 LINK DAFTAR :https://lanjutmasuks138 .click/login/</t>
   </si>
   <si>
-    <t>api khusus sedia hot game ggsoft slt api modal ribu hasil juta tabrak nikmat utama main slt uang sayap link daftar {LINK}</t>
+    <t>api sedia game hot spesial ggsoft slt api modal rb hasil juta tabrak nikmat uang main slt uang sayap taut daftar {LINK} click login</t>
   </si>
   <si>
     <t>Hmm</t>
@@ -149,7 +156,7 @@
     <t>Widih gacor nya bener bener mantap #MAHASLOT WD terus Tampa Rungkat mantap</t>
   </si>
   <si>
-    <t>widih gacor mantap banget mahaslot wd tampa rungkat mantap banget</t>
+    <t>widih gacor mantap banget mahaslot wd mantap</t>
   </si>
   <si>
     <t>𝐒 𝐎 𝐋 𝐔 𝐒 𝐈 𝐖 𝐈 𝐍 𝐫𝐞𝐤𝐨𝐦𝐞𝐧𝐝𝐚𝐬𝐢 𝐲𝐚𝐧𝐠 𝐬𝐚𝐧𝐠𝐚𝐭 𝐚𝐦𝐚𝐧 𝐭𝐞𝐫𝐩𝐞𝐫𝐜𝐚𝐲𝐚</t>
@@ -158,13 +165,25 @@
     <t>s o l u s i w i n rekomendasi aman percaya</t>
   </si>
   <si>
+    <t>Info situs gacor dong inbox kalau ada</t>
+  </si>
+  <si>
+    <t>info situs gacor silah inbox</t>
+  </si>
+  <si>
     <t>Baru</t>
   </si>
   <si>
     <t>GK ragu klo mau milih itu ya tetap mahaslot lah yg gacor nya GK ketulungan barusan WD lagi coy 8jt #MAHASLOT</t>
   </si>
   <si>
-    <t>ayal pilih mahaslot sial wd juta mahaslot</t>
+    <t>ragu pilih mahaslot sial wd juta mahaslot</t>
+  </si>
+  <si>
+    <t>Wd nya sdh lancar ya bosku</t>
+  </si>
+  <si>
+    <t>wd nya lancar bos</t>
   </si>
   <si>
     <t>Superspin
@@ -202,6 +221,12 @@
     <t>percaya ramatogel percaya ramatogel percaya ramatogel percaya ramatogel percaya ramatogel</t>
   </si>
   <si>
+    <t>Hhh ga bisa narik</t>
+  </si>
+  <si>
+    <t>h tarik</t>
+  </si>
+  <si>
     <t>super oke 𝗥𝗔𝗠𝗔𝗧𝗢𝗚𝗘𝗟
 super oke 𝗥𝗔𝗠𝗔𝗧𝗢𝗚𝗘𝗟
 super oke 𝗥𝗔𝗠𝗔𝗧𝗢𝗚𝗘𝗟
@@ -224,7 +249,7 @@
 LINK DAFTAR :https://lanjutmasuks138 .click/login/</t>
   </si>
   <si>
-    <t>api khusus sedia game hot ggsoft slot api modal ribu hasil juta tabrak nikmat utama main slot uang sayap link daftar {LINK}</t>
+    <t>api sedia game panas khusus ggsoft slot api modal rb hasil juta tabrak nikmat uang main slot uang sayap taut daftar {LINK} click login</t>
   </si>
   <si>
     <t>Wajib di coba sih di 💥𝘽𝙀𝙍𝘼𝙉𝙄𝙒𝙄𝙉💥. mBY</t>
@@ -233,6 +258,12 @@
     <t>wajib coba tabrak beraniwin tabrak mby</t>
   </si>
   <si>
+    <t>Depo awal sebelum wd 👍</t>
+  </si>
+  <si>
+    <t>deposit wd jempol</t>
+  </si>
+  <si>
     <t>Gak perlu skill khusus buat sukses di💥𝘽𝙀𝙍𝘼𝙉𝙄𝙒𝙄𝙉💥. rZ</t>
   </si>
   <si>
@@ -242,7 +273,7 @@
     <t>mahjong skketernya keluar mulu say di 💥𝘽𝙀𝙍𝘼𝙉𝙄𝙒𝙄𝙉💥 Cja</t>
   </si>
   <si>
-    <t>pencar mahjong tabrak beraniwin tabrak ngobrol</t>
+    <t>pencar mahjong tabrak beraniwin tabrak chat</t>
   </si>
   <si>
     <t>Bonus bulanan sudah cair 💥𝘽𝙀𝙍𝘼𝙉𝙄𝙒𝙄𝙉💥, waktunya menikmati hasil  NNQ</t>
@@ -260,7 +291,7 @@
     <t>Ayo, bre, raih kemenangan besar di 🔥𝘽𝙀𝙍𝘼𝙉𝙄𝙒𝙄𝙉🔥 bersama-sama!😎 TLt</t>
   </si>
   <si>
-    <t>yuk gan raih menang api beraniwin api wajah kacamata hitam tlt</t>
+    <t>ayo gan raih menang api beraniwin api wajah kacamata hitam tlt</t>
   </si>
   <si>
     <t>cek google 🎂 🔥𝘽𝙀𝙍𝘼𝙉𝙄𝙒𝙄𝙉🔥 🎂 Mantap bosku, , makasih uda kasih saran main di situs ini mcm</t>
@@ -272,16 +303,19 @@
     <t>Kiamat sudah dekat</t>
   </si>
   <si>
+    <t>kiamat</t>
+  </si>
+  <si>
     <t>tes aja PG SOFT nya 𝗛𝗜𝗠𝗔𝗟𝗔𝗬𝗔𝟰𝗗 maseeh gampang banget turun scatter sama perkalian nya</t>
   </si>
   <si>
-    <t>coba pg soft himalayad mudah banget scatter kali</t>
+    <t>test pg soft nya himalayad mudah banget scatter kali</t>
   </si>
   <si>
     <t>mantul eng situs #MAHASLOT gas abiz di jamin 100% JP guys buru' cobain dahh</t>
   </si>
   <si>
-    <t>situs ind manfaat mahaslot abiz gas jamin jp guys buru coba</t>
+    <t>situs eng manfaat mahaslot abiz gas jamin jp guys buru coba</t>
   </si>
   <si>
     <t>Gas</t>
@@ -311,7 +345,7 @@
     <t>si mbah zeus ngamuk wingi😁, metu x500 wingi di kei karok situs 🔥𝘽𝙀𝙍𝘼𝙉𝙄𝙒𝙄𝙉🔥😁 YHH</t>
   </si>
   <si>
-    <t>mbah zeus marah wing wajah gembira mata bahagia metu x wing situs kei karok api beraniwin api wajah gembira mata bahagia yhh</t>
+    <t>mbah zeus marah marah wing wajah gembira mata bahagia metu x wing situs kei karok api beraniwin api wajah gembira mata bahagia yhh</t>
   </si>
   <si>
     <t>ngangkat lumayan diBONBON777 main zeus 1000 tadi</t>
@@ -350,13 +384,13 @@
     <t>Andalan banget jni #MAHASLOT bener bener dikasih jp terus mantap</t>
   </si>
   <si>
-    <t>andal mahaslot jp</t>
+    <t>handal banget mahaslot jp bagus</t>
   </si>
   <si>
     <t>Abis WD 15jt nih bos senggol dong #MAHASLOT  gacor parah ey</t>
   </si>
   <si>
-    <t>habis wd juta bos kena mahaslot jelek banget ey</t>
+    <t>habis wd juta bos kesal mahaslot parah ey</t>
   </si>
   <si>
     <t>Kumpulan svip, free 20k bonus ikat akun👍
@@ -376,7 +410,7 @@
 https://cutt.ly/SrWSqL1G</t>
   </si>
   <si>
-    <t>koleksi svip bonus ikat akun gratis k jempol svip {LINK} svip {LINK} svip {LINK} svip {LINK} putar super api {LINK} svip {LINK} svip {LINK}</t>
+    <t>koleksi svip bonus ikat akun gratis rb jempol svip {LINK} svip {LINK} svip {LINK} svip {LINK} putar super api {LINK} svip {LINK} svip {LINK}</t>
   </si>
   <si>
     <t>kenapa main di mana pun susah menang.sekali cobain saran temen di 𝐩𝐥𝐚𝐳𝐚𝟒𝐃 di kasih jp</t>
@@ -407,13 +441,13 @@
     <t>Situs terpercaya tergacor bro cobain dah gas #MAHASLOT dikasih WD Mulu mantap</t>
   </si>
   <si>
-    <t>situs tergacor percaya gan coba gas mahaslot kasih wd mulu mantap</t>
+    <t>situs tergacor percaya gan coba gas mahaslot kasih wd mantap</t>
   </si>
   <si>
     <t>EVENT SPESIAL BOMBANZA PRAGMATIC PLAY!         Putaran turun X25, X50, bahkan X100?         Jangan lewatkan kesempatan langka ini!         Dapatkan bonus hingga 10 juta rupiah hanya di MACAUSLOT188!         Main santai, cuan maksimal!         👉 https://bit.ly/43XW7l9 #EventBombanza #PragmaticPlay #Bonus10Juta #MACAUSLOT188 #PutaranX100</t>
   </si>
   <si>
-    <t>acara khusus bombanza pragmatic play bulat x x x langka bonus juta rupiah macauslot main santai maksimal untung arah kanan {LINK} eventbombanza pragmaticplay bonusjuta macauslot putaranx</t>
+    <t>acara spesial bombanza pragmatic play putar x x x langka bonus juta rupiah macauslot main santai untung maksimal arah kanan {LINK} eventbombanza pragmaticplay bonusjuta macauslot putaranx</t>
   </si>
   <si>
     <t>🥰 PROVIDER BARUNYA GGSOFT #SLOT138
@@ -423,13 +457,13 @@
 LINK DAFTAR :https://lanjutmasuks138 .click/login/</t>
   </si>
   <si>
-    <t>wajah senyum hati sedia ggsoft slot api nikmat acara khusus ggsoft bonus multiplikasi fantastis tabrak main nikmat utama mudah slot link daftar {LINK}</t>
+    <t>wajah senyum hati sedia ggsoft slot api nikmat acara ggsoft spesial bonus kelipat fantastis tabrak main nikmat uang mudah slot taut daftar {LINK} click login</t>
   </si>
   <si>
     <t>Super Bagus #𝗛𝗦𝗪𝗜𝗡𝟱𝟱💎Very good good💯  🌊𝗛𝗦𝗪𝗜𝗡𝟱𝟱🌊𝑺𝒖𝒑𝒆𝒓 𝒃𝒂𝒊𝒌💯🌊𝗛𝗦𝗪𝗜𝗡𝟱𝟱🌊SUPER BAGUS                                        𝗛𝗦𝗪𝗜𝗡𝟱𝟱                                        SEMOGA REJEKINYA NULAR BOS 🌠🌠𝑺𝒖𝒑𝒆𝒓 𝒃𝒂𝒊𝒌💯🌊𝗛𝗦𝗪𝗜𝗡𝟱𝟱🌊𝑺𝒖𝒑𝒆𝒓 𝒃𝒂𝒊𝒌💯🌊𝗛𝗦𝗪𝗜𝗡𝟱𝟱🌊Very good good💯  🌊𝗛𝗦𝗪𝗜𝗡𝟱𝟱🌊SUPER BAGUS                                       𝗛𝗦𝗪𝗜𝗡𝟱𝟱                                          SEMOGA REJEKINYA NULAR BOS 🌠🌠</t>
   </si>
   <si>
-    <t>bagus hswin batu permata bagus bagus nilai ratus ombak hswin ombak super nilai ratus ombak hswin ombak super bagus hswin moga untung null boss bintang jatuh bintang jatuh super nilai ratus ombak hswin ombak super nilai ratus ombak hswin ombak bagus bagus nilai ratus ombak hswin ombak bagus hswin moga rezeki null boss bintang jatuh bintang jatuh</t>
+    <t>bagus hswin batu permata bagus bagus nilai ratus ombak hswin ombak super nilai ratus ombak hswin ombak super bagus hswin moga untung tular bos bintang jatuh bintang jatuh super nilai ratus ombak hswin ombak super nilai ratus ombak hswin ombak bagus bagus nilai ratus ombak hswin ombak bagus hswin moga untung tular bos bintang jatuh bintang jatuh</t>
   </si>
   <si>
     <t>น่ารักมากเลยค่ะ.#𝗛𝗦𝗪𝗜𝗡𝟱𝟱  Super Bagus  𝗛𝗦𝗪𝗜𝗡𝟱𝟱  💎Super Bagus #💎Very good good💯 
@@ -437,7 +471,7 @@
 🌊𝗛𝗦𝗪𝗜𝗡𝟱𝟱 🌊SUPER BAGUS                                           𝗛𝗦𝗪𝗜𝗡𝟱𝟱                                      SEMOGA REJEKINYA NULAR BOS 🌠🌠</t>
   </si>
   <si>
-    <t>hswin super bagus hswin batu permata super bagus batu permata bagus bagus nilai ratus ombak hswin ombak super nilai ratus ombak hswin ombak super bagus hswin moga untung null boss bintang jatuh bintang jatuh super nilai ratus ombak hswin ombak super nilai ratus ombak hswin ombak bagus bagus nilai ratus ombak hswin ombak super bagus hswin untung null boss bintang jatuh bintang jatuh</t>
+    <t>hswin bagus hswin batu permata bagus batu permata bagus bagus nilai ratus super bagus nilai ratus ombak hswin ombak bagus bagus nilai ratus ombak hswin ombak bagus hswin moga untung tular bos bintang jatuh bintang jatuh</t>
   </si>
   <si>
     <t>Super Bagus 𝗛𝗦𝗪𝗜𝗡𝟱𝟱
@@ -452,7 +486,7 @@
     <t>Super Bagus #𝗛𝗦𝗪𝗜𝗡𝟱𝟱 🎱𝚂𝚊𝚗𝚐𝚊𝚝 𝙱𝚊𝚐𝚞𝚜🖤 𝗛𝗦𝗪𝗜𝗡𝟱𝟱 🎱Super Bagus 𝗛𝗦𝗪𝗜𝗡𝟱𝟱 🎱Super Bagus 𝗛𝗦𝗪𝗜𝗡𝟱𝟱🎱𝚂𝚊𝚗𝚐𝚊𝚝 𝙱𝚊𝚐𝚞𝚜🖤 𝗛𝗦𝗪𝗜𝗡𝟱𝟱 Super Baguss 𝗛𝗦𝗪𝗜𝗡𝟱𝟱 Super Hebat 𝗛𝗦𝗪𝗜𝗡𝟱𝟱  Super Baik 𝗛𝗦𝗪𝗜𝗡𝟱𝟱 สวยงามมาก🔥 💥 𝐝𝐢𝐤𝐚𝐬𝐢𝐡 𝐭𝐞𝐫𝐮𝐬 𝐤𝐞𝐫𝐞𝐧 𝐬𝐞𝐤𝐚𝐥𝐢   𝐉𝐚𝐲𝐚 𝐬𝐞𝐥𝐚𝐥𝐮 🎱🎱🎱🎱🎱🎱𝗛𝗦𝗪𝗜𝗡𝟱𝟱 👍</t>
   </si>
   <si>
-    <t>bagus hswin biliar bola bagus hati hitam hswin biliar bola bagus hswin biliar bola bagus hswin biliar bola bagus hati hitam hswin super bagus hswin super hebat hswin super bagus hswin keren jayb biliar bola biliar bola biliar bola biliar bola biliar bola biliar bola hswin jempol</t>
+    <t>bagus hswin biliar bola bagus hati hitam hswin biliar bola bagus hswin biliar bola bagus hswin biliar bola bagus hati hitam hswin bagus hswin bagus hswin bagus hswin keren jayb biliar bola biliar bola biliar bola biliar bola biliar bola biliar bola hswin jempol</t>
   </si>
   <si>
     <t>Bingung cari situs aman terpercaya &amp; RTP tinggi
@@ -461,7 +495,7 @@
 GasBossku^^</t>
   </si>
   <si>
-    <t>bingung cari situs aman percaya rtp qqmamibet solusi bos link alternatif qqmamibet bos gas</t>
+    <t>bingung cari situs aman percaya rtp qqmamibet solusi bos taut alternatif qqmamibet bos gas</t>
   </si>
   <si>
     <t>Duite</t>
@@ -479,7 +513,7 @@
 PENCARIAN GOOGLE : SITUSWD</t>
   </si>
   <si>
-    <t>bonus begadang anggota member slot khusus setor qris beli gratis ip gratis slot cari google sitewd</t>
+    <t>bonus begadang anggota khusus member slot setor qris putar beli gratis ip gratis slot cari google situswd</t>
   </si>
   <si>
     <t>Apk Gacor  INA77 yang  Sudah terliris lama harian nya sangat tinggi hanya depo 100K bisa dptkan harian yang melipat ganda
@@ -487,27 +521,27 @@
 https://www.in858.com?chn=bnRfaW5hNzc3&amp;id=MzM2NTI3ODY=</t>
   </si>
   <si>
-    <t>gacor ina apk rilis milik deposit deposit k ganda taut unduh {LINK}</t>
+    <t>gacor ina apk rilis deposit deposit k ganda taut unduh {LINK}</t>
   </si>
   <si>
     <t>LINK ANTI RUNGKAT DAN PASTI JP 
  cari di google : slot gacor --hkb77</t>
   </si>
   <si>
-    <t>link anti retak jp cari google slot gacor hkb</t>
+    <t>linknya anti crack jp cari google slot gacor hkb</t>
   </si>
   <si>
     <t>Kumpulan Apk wd lancar 👍
 https://biolinky.co/apkpilihan</t>
   </si>
   <si>
-    <t>koleksi wd apk lancar jempol {LINK} pilih</t>
+    <t>koleksi apk wd jalan lancar jempol {LINK} pilih</t>
   </si>
   <si>
     <t>gak perlu banyak cakap kalau mau situs ini #Jeruk123 🍊gacor parah BG</t>
   </si>
   <si>
-    <t>bicara situs jeruk buah jeruk bad gacor bg</t>
+    <t>bicara situs jeruk buah jeruk jelek banget</t>
   </si>
   <si>
     <t>𝐇𝐚𝐧𝐲𝐚 𝐝𝐢 𝐒𝐎𝐋𝐔𝐒𝐈𝐖𝐈𝐍 𝐲𝐚𝐧𝐠 𝐦𝐮𝐝𝐚𝐡 𝐝𝐚𝐩𝐚𝐭 𝐜𝐮𝐚𝐧.
@@ -522,13 +556,13 @@
     <t>Dikasih WD lagi gue bro mantap MAHASLOT royal parah #MAHASLOT</t>
   </si>
   <si>
-    <t>ane kasih wd gan mahaslot jelek banget royal mahaslot</t>
+    <t>ane kasih wd gan mantap mahaslot royal jelek banget mahaslot</t>
   </si>
   <si>
     <t>Abis WD 20jt dimahaslot bro senggol dong mantap #MAHASLOT</t>
   </si>
   <si>
-    <t>habis wd juta mahaslot gan senggol mantap mahaslot</t>
+    <t>wd juta mahaslot gan nyenggolnya mantap mahaslot</t>
   </si>
   <si>
     <t>Lucky72.
@@ -603,7 +637,7 @@
 ━━━━━━━━━━━━━━━━━━━━━━━━━━</t>
   </si>
   <si>
-    <t>mudah rungkad gabung yodad wajah materialistis minimal deposit jamin menang wajah senyum lebar mata hati rambu stop deposit main jackpot rambu stop gabung rambu stop situs main slot populer yodad situs percaya game sedia slot togel tembak ikan kasino langsung buku olahraga perawan ayam paku tanda tombol id akses game tanda centang putih tebal keras suara promo bonus anggota bonus gulir buku olahraga referensi kompetisi tebak angka d paku tanda link grup facebook tanda dolar tebal minimum deposit rp tanda dolar tebal minimum tari rp tanda dolar tebal minimum bet togel rp silver tanda dolar tebal sedia taruh slot perak dukung deposit wajik biru via qris wajik biru pulsa telkomsel xl axis wajik biru e wallet dana gopay linkaja ovo shoppe wajik biru jenis bank</t>
+    <t>mudah gabung yodad wajah materialistis minimal deposit jamin menang wajah senyum lebar mata hati rambu stop deposit main jackpot rambu stop gabung rambu stop situs main slot tergacor yodad situs percaya main sedia slot togel tembak ikan kasino langsung buku olahraga sabung ayam paku tanda tombol id akses game tanda centang putih tebal keras suara promosi bonus anggota bonus gulir buku olahraga referensi lomba tebak angka d paku tanda taut grup facebook tanda dolar tebal minimum deposit rp tanda dolar tebal minimum tari rp tanda dolar tebal minimum taruh togel rp perak tanda dolar tebal sedia slot taruh perak dukung setor wajik biru qris wajik biru kredit telkomsel xl axis wajik biru e wallet dana gopay linkaja ovo shoppe wajik biru jenis bank</t>
   </si>
   <si>
     <t>super mantap👉 𝐑𝐀𝐌𝐀𝐓𝐎𝐆𝐄𝐋 
@@ -669,7 +703,7 @@
 - PROSES DP &amp; WD HANYA 1-3 menit</t>
   </si>
   <si>
-    <t>salam maxwin pedrod situs slot gacor no indonesia rekomendasi website proses cepat cepat promosi pedrod lingkar merah bonus anggota lingkar merah bonus deposit lingkar merah bonus turnover minggu lingkar merah bonus cashback minggu lingkar merah bonus referensi arah kanan bonus menang buyspin freespin arah kanan bonus scatter murni game pragmatis arah kanan bonus scatter murni mahjong arah kanan bonus koi gate jejer jejer arah kanan bonus multiplikasi petir arah kanan bonus beli winstreak arah kanan bonus tantang wd slot bonus m arah kanan bonus menang ayam arah kanan bonus sepakbola mix parlay arah kanan kompetisi lotere swiss singapura taiwan nilai ratus layan jam nilai ratus layan cepat aman ribet nonstop min dp bank min dp e money min dp xl tsel pulsa proses dp wd menit</t>
+    <t>salam maxwin pedrod situs slot gacor no indonesia situs web rekomendasi proses cepat bebas repot promo pedrod lingkar merah bonus anggota lingkar merah bonus setor lingkar merah bonus turnover minggu lingkar merah bonus cashback minggu lingkar merah bonus referensi arah kanan bonus menang buyspin freespin arah kanan bonus pencar murni game pragmatis arah kanan bonus pencar murni mahjong arah kanan bonus koi gate baris baris arah kanan bonus kali kilat arah kanan bonus putar beli winstreak arah kanan challenge bonus wd slot bonus juta arah kanan bonus winstreak sabung ayam arah kanan bonus parlay campur bola arah kanan kompetisi lotere swiss singapura taiwan nilai ratus layan jam nilai ratus layan nonstop cepat aman bebas repot min dp bank min deposit e money min dp xl kredit tsel proses dp wd butuh menit</t>
   </si>
   <si>
     <t>น่ารักมากเลยค่ะ.#𝘽𝘿𝙏𝙊𝙏𝙊𝟮𝟭  Super Bagus  𝗯𝗱𝘁𝗼𝘁𝗼𝟮𝟭  💎Super Bagus #💎Very good good💯 
@@ -677,13 +711,13 @@
 🌊𝗯𝗱𝘁𝗼𝘁𝗼𝟮𝟭 🌊SUPER BAGUS                                        #   𝗯𝗱𝘁𝗼𝘁𝗼𝟮𝟭                                       SEMOGA REJEKINYA NULAR BOS 🌠🌠</t>
   </si>
   <si>
-    <t>naarakmaakelykha bdtoto super bagus bdtoto batu permata super bagus batu permata bagus bagus nilai ratus ombak bdtoto ombak super nilai ratus ombak bdtoto ombak super bagus bdtoto selamat hasil boss bintang jatuh bintang jatuh super nilai ratus ombak bdtoto ombak super nilai ratus ombak bdtoto ombak bagus nilai ratus ombak bdtoto ombak super bagus bdtoto moga rezeki noll boss bintang jatuh bintang jatuh</t>
+    <t>naarakmaakelykha bdtoto super bagus bdtoto batu permata bagus batu permata bagus bagus nilai ratus ombak bdtoto ombak super nilai ratus ombak bdtoto ombak super bagus bdtoto moga rezeki tular bos bintang jatuh bintang jatuh super nilai ratus ombak bdtoto ombak super nilai ratus ombak bdtoto ombak bagus bagus nilai ratus ombak bdtoto ombak super bagus bdtoto moga untung tular bos bintang jatuh bintang jatuh</t>
   </si>
   <si>
     <t>Super Bagus  #𝘽𝘿𝙏𝙊𝙏𝙊𝟮𝟭💎Very good good💯  🌊𝗯𝗱𝘁𝗼𝘁𝗼𝟮𝟭🌊𝑺𝒖𝒑𝒆𝒓 𝒃𝒂𝒊𝒌💯🌊𝗯𝗱𝘁𝗼𝘁𝗼𝟮𝟭🌊SUPER BAGUS                                        #𝗯𝗱𝘁𝗼𝘁𝗼𝟮𝟭                                         SEMOGA REJEKINYA NULAR BOS 🌠🌠𝑺𝒖𝒑𝒆𝒓 𝒃𝒂𝒊𝒌💯🌊𝗯𝗱𝘁𝗼𝘁𝗼𝟮𝟭🌊𝑺𝒖𝒑𝒆𝒓 𝒃𝒂𝒊𝒌💯🌊𝗯𝗱𝘁𝗼𝘁𝗼𝟮𝟭🌊Very good good💯  🌊𝗯𝗱𝘁𝗼𝘁𝗼𝟮𝟭🌊SUPER BAGUS                                        #𝗯𝗱𝘁𝗼𝘁𝗼𝟮𝟭                                          SEMOGA REJEKINYA NULAR BOS 🌠🌠</t>
   </si>
   <si>
-    <t>super bagus bdtoto batu permata bagus bagus nilai ratus ombak bdtoto ombak super nilai ratus ombak bdtoto ombak super bagus bdtoto selamat untung bos bintang jatuh bintang jatuh super nilai ratus ombak bdtoto ombak super nilai ratus ombak bdtoto ombak bagus nilai ratus ombak bdtoto ombak bagus bdtoto moga rezeki null boss bintang jatuh bintang jatuh</t>
+    <t>bagus bdtoto batu permata bagus bagus nilai ratus ombak bdtoto ombak super nilai ratus ombak bdtoto ombak super bagus bdtoto moga untung tular bos bintang jatuh bintang jatuh super nilai ratus ombak bdtoto ombak super nilai ratus ombak bdtoto ombak bagus bagus nilai ratus ombak bdtoto ombak bagus bdtoto moga untung tular bos bintang jatuh bintang jatuh</t>
   </si>
   <si>
     <t>Super Bagus 𝘽𝘿𝙏𝙊𝙏𝙊𝟮𝟭
@@ -714,7 +748,7 @@
     <t>Pantes di apotek ga jual obat ginian yg ada cuman di mari  aja lur wkw</t>
   </si>
   <si>
-    <t>apotek jual obat haha</t>
+    <t>apotik jual obat haha</t>
   </si>
   <si>
     <t>Cek link dibawah 👇👇👇
@@ -722,7 +756,7 @@
 https://biolinky.co/apkpilihan</t>
   </si>
   <si>
-    <t>cek link koleksi wd apk lancar jempol {LINK} pilih</t>
+    <t>cek link koleksi apk wd jalan lancar jempol {LINK} pilih</t>
   </si>
   <si>
     <t>Mau kasih info dikit, 𝗕𝗔𝗬𝗔𝗠𝟭𝟮𝟯 lagi rame banget, yang main pada panen menang.</t>
@@ -735,6 +769,9 @@
   </si>
   <si>
     <t>Hmmm</t>
+  </si>
+  <si>
+    <t>hm</t>
   </si>
   <si>
     <t>Tt789🥇
@@ -786,7 +823,7 @@
 🙏🏻TERIMA KASIH SALAM HOKI KOITOTO🙏🏻</t>
   </si>
   <si>
-    <t>megafon promo koitoto megafon simbol jepang bonus anggota simbol jepang referensi bonus teman simbol jepang bonus habanero batas simbol jepang bonus referensi simbol jepang gratis chip rp simbol jepang bonus slot cashback simbol jepang bonus cashback game langsung simbol jepang bonus turnover slot simbol jepang bonus main langsung simbol jepang bonus turnover climbing hadiah juta simbol jepang bonus gratis simbol jepang bonus beli simbol jepang bonus minggu koitoto sedia x minggu bossku senin bonus idn ply rollingan bonus rollingan live casino pragmatic play selasa climb turn over slot m rabu game langsung cashback kamis bonus rolligan slot jumat bonus cashback live pragmatic play casino sabtu bonus cashback slot arah kanan pasar lotere arah kanan min taruh perak arah kanan min deposit rb arah kanan min tari ribu arah kanan jenis taruh taruh diskon taruh penuh taruh hadiah taruh bb arah kanan hadiah bayar arah kanan hadiah lotere arah kanan garis investasi gratis arah kanan tutup hong kong arah kanan kompetisi togel arah kanan acara slot ayo bossku daftar id gamesmu koitoto lipat tangan warna kulit cerah terima kasih salam hoki koitoto lipat tangan warna kulit cerah</t>
+    <t>megafon promo koitoto megafon simbol jepang bonus anggota simbol jepang undang bonus teman simbol jepang bonus habanero henti simbol jepang bonus rujuk simbol jepang gratis chip rp simbol jepang bonus slot cashback simbol jepang bonus uang main langsung simbol jepang bonus ganti slot simbol jepang bonus turnover main langsung simbol jepang bonus daki omset hadiah juta simbol jepang bonus putar gratis simbol jepang beli bonus putar simbol jepang bonus minggu koitoto x minggu bos senin bonus gulir idn ply bonus gulir pragmatic play kasino live selasa omset slot juta rabu cashback main langsung kamis bonus slot rolligan jumat bonus cashback kasino langsung main pragmatis sabtu bonus cashback slot arah kanan pasar lotere arah kanan min taruh perak arah kanan min deposit rb arah kanan min tari rb arah kanan jenis jenis taruh taruh diskon taruh penuh taruh hadiah taruh bb arah kanan hadiah bayar arah kanan hadiah lotere arah kanan jalur investasi gratis arah kanan tutup taruh hong kong arah kanan kompetisi togel arah kanan slot acara yuk bos daftar id game koitoto lipat tangan warna kulit cerah terima kasih salam koitoto hockey lipat tangan warna kulit cerah</t>
   </si>
   <si>
     <t>Meledak Gas bosku</t>
@@ -822,19 +859,19 @@
     <t>klo maen cari BO jelas itu ke 🌟𝐊𝗨𝐒𝗨𝐌𝗔𝐓𝟬𝐓𝟬🌟 aja bos ku . Gw uda jelajahi bnyk web , Cuma di 🌟𝐊𝗨𝐒𝗨𝐌𝗔𝐓𝟬𝐓𝟬🌟 aja kesbek, ribete, event, sama bonus paling unggul yg paling penting webnya jelas &amp; resmi jd mau wd berapapun dibayar. Coba cek sendiri deh</t>
   </si>
   <si>
-    <t>main cari bo bos website jelajah bintang sinar kusumatt bintang sinar kerepot event bonus unggul websitenya resmi bayar bayar coba periksa</t>
+    <t>main cari bos bos website jelajah bintang sinar kusumatt bintang sinar repot repot event bonus unggul websitenya resmi bayar bayar coba periksa</t>
   </si>
   <si>
     <t>Akhirnya aku ikut ngerasaain rasanya mekswin, terima kasih beeut 𝐊𝗨𝐒𝗨𝐌𝗔𝐓𝟬𝐓𝟬 uda modalin aku buat buka warung bersyukur banget dahh 🙏🙏</t>
   </si>
   <si>
-    <t>cita maxwin terima kasih belut kusumatt modal buka toko terima kasih lipat tangan lipat tangan</t>
+    <t>maxwin terima kasih belut</t>
   </si>
   <si>
     <t>Andalan bro buat saldo selalu penuh #MAHASLOT emng gacor gas cobain dah</t>
   </si>
   <si>
-    <t>andal warna biru biar saldo penuh mahaslot beneran kena bensin coba deh</t>
+    <t>andal biru bikin saldo penuh mahaslot sungguh fungsi coba</t>
   </si>
   <si>
     <t>𝐒 𝐎 𝐋 𝐔 𝐒 𝐈 𝐖 𝐈 𝐍 𝐫𝐞𝐤𝐨𝐦𝐞𝐧𝐝𝐚𝐬𝐢 𝐲𝐚𝐧𝐠 𝐬𝐚𝐧𝐠𝐚𝐭 𝐚𝐦𝐚𝐧 𝐭𝐞𝐫𝐩𝐞𝐫𝐜𝐚𝐲𝐚
@@ -870,7 +907,7 @@
     <t>Nyenengin banget situs ⭐𝐄𝐑𝐀𝐉𝐏⭐ bray full senyum awak di buat nya   m</t>
   </si>
   <si>
-    <t>situs seru banget bintang medium putih erajp bintang medium putih gan penuh senyum hasil</t>
+    <t>situs seru banget bintang medium putih erajp bintang medium putih bro senyum penuh hasil</t>
   </si>
   <si>
     <t>Tadi iseng coba ikutin saran teman gw main di #mahaslot ternyata beneran di kasih J3p3, makasih bro 😜</t>
@@ -894,7 +931,7 @@
     <t>Aku sambil rebahan jg dapat uang jajan dari 𝐊𝗨𝐒𝗨𝐌𝗔𝐓𝟬𝐓𝟬, modarl 50rb doang main ga sampe 15 menit cair 900rb wkwkwk lumayan lah buat isi bensin sama rokok hehehe</t>
   </si>
   <si>
-    <t>rebah uang jajan kusumatt modal rb main menit cair rb hahaha lumayan isi bensin rokok hehehe</t>
+    <t>rebah uang jajan kusumatt modal rb main menit bayar rb hahaha lumayan isi bensin rokok hehehe</t>
   </si>
   <si>
     <t>Terbukti main di 🌟#BALIPLAY🌟 tidak merasa takut karna sistemnya fair play💯% dan banyak fitur terbaik di bidangnya pantesan semua orang jadi betah main disini💸💸</t>
@@ -919,7 +956,7 @@
     <t>Asli kagak boong bro barusan WD di MAHASLOT bener bener gacor parah sih #MAHASLOT</t>
   </si>
   <si>
-    <t>beneran gak bohong gan wd mahaslot beneran gak fungsi mahaslot</t>
+    <t>asli palsu gan wd mahaslot jelek banget jelek banget mahaslot</t>
   </si>
   <si>
     <t>Fix gak nyesel! 💦𝐄𝐑𝐀𝐉𝐏💦 selalu kasih kejutan seru!</t>
@@ -955,19 +992,19 @@
     <t>Seru abis! Setia banget sama ⭐💙𝐄𝐑𝐀𝐉𝐏💙⭐ sejak awal main ada aja ketujuan nya Y</t>
   </si>
   <si>
-    <t>senang setia banget bintang medium putih hati biru erajp hati biru bintang medium putih main gol y</t>
+    <t>tarik setia banget bintang medium putih hati biru erajp hati biru bintang medium putih main udah gol ya</t>
   </si>
   <si>
     <t>Lumayan depo main bonus 100% 50+50 all slot bisa wd segini, situs nya #𝐌𝐄𝐕𝐈𝐔𝐒𝐓𝐎𝐓𝐎</t>
   </si>
   <si>
-    <t>lumayan deposit main bonus slot bayar situs meviustoto</t>
+    <t>deposit bagus bonus main slot bayar situs meviustoto</t>
   </si>
   <si>
     <t>asli awalnya aku kira bakal rungkad ternyata dikasih di akhir naganya pecah diBONBON777</t>
   </si>
   <si>
-    <t>beranta nyata dragonbreaking bonbon</t>
+    <t>lengkap nyata dragonbreaking bonbon</t>
   </si>
   <si>
     <t>Buset hoky benerr dah Setiap main di ⭐𝐄𝐑𝐀𝐉𝐏⭐  O</t>
@@ -979,7 +1016,7 @@
     <t>Baru dapat dividen dari 💥𝘽𝙀𝙍𝘼𝙉𝙄𝙒𝙄𝙉💥, uang pasif memang menyenangkan. dOD</t>
   </si>
   <si>
-    <t>dividen tabrak beraniwin tabrak passive money sungguh senang laku</t>
+    <t>dividen tabrak beraniwin tabrak passive money seru banget dod</t>
   </si>
   <si>
     <t>bosen x250 turun terus main kakek di situs 💦𝐄𝐑𝐀𝐉𝐏💦 j</t>
@@ -991,7 +1028,7 @@
     <t>Emang gak ada yang se-mantep💦𝐄𝐑𝐀𝐉𝐏💦 deh. C</t>
   </si>
   <si>
-    <t>stabil keringat erajp keringat c</t>
+    <t>hebat c</t>
   </si>
   <si>
     <t>ku pikir bakalan di sedot bg tau nya di kasih up berlipat lipat sama mj 𝐌𝐄𝐕𝐈𝐔𝐒𝐓𝐎𝐓𝐎</t>
@@ -1003,7 +1040,7 @@
     <t>HIdup lagi cape-capenya malah dikasih kejutan sama 𝗗𝗼𝗶𝟴𝟴, uang makan sama bensin bulan ini aman terkendali wkwkwk</t>
   </si>
   <si>
-    <t>hidup capek banget kasih kejut doi uang makan bensin kendali hahaha</t>
+    <t>capek banget hidup kasih kejut doi uang makan bensin aman kendali hahaha</t>
   </si>
   <si>
     <t>tempat main terbaik dan mudah cuan hanya di 🔥𝐒𝐆𝐀𝟑𝟑𝟖🔥 benar paling gacor</t>
@@ -1015,7 +1052,7 @@
     <t>Halo bosku 🤗! Bosan main rungkat? 🤔 Aku bisa bantu kamu *menang*, *CLAIM* *SALDO* *GRATIS* *85K* 🤑! Mainkan di https://batagorgoreng.net/ 📊, yuk coba keberuntunganmu 🎉! 🤑💸</t>
   </si>
   <si>
-    <t>halo bos wajah peluk bosan main rungkat wajah pikir bantu menang klaim saldo gratis k wajah materialistis main {LINK} diagram batang yuk coba untung party popper wajah materialistis uang sayap</t>
+    <t>halo bos wajah peluk bosan main rungkat wajah pikir bantu menang klaim saldo gratis rb wajah materialistis main {LINK} diagram batang yuk coba untung party popper wajah materialistis uang sayap</t>
   </si>
   <si>
     <t>Raihla Kemenangan dan Pecahan Perkalian Hanya Di PLAZABOLA
@@ -1024,7 +1061,7 @@
 LINK VIP 1 : https://shorturl.at/tdCMf</t>
   </si>
   <si>
-    <t>raih menang kali pecah plazabola nyaman percaya bukti gacor link alternatif plazabola taut vip {LINK}</t>
+    <t>raih menang kali pecah plazabola nyaman percaya bukti work link alternatif plazabola taut vip {LINK}</t>
   </si>
   <si>
     <t>Sp777🥇
@@ -1049,25 +1086,25 @@
 https://h5.l77723.top?chn=bDcwMzA=&amp;id=Nzc5MzExODky</t>
   </si>
   <si>
-    <t>sp medali emas {LINK} putarrp medali emas {LINK} vita medali emas {LINK} medali emas {LINK} mewah medali emas {LINK} sd medali emas {LINK} sia medali emas {LINK} st medali emas {LINK} rppemenang medali militer {LINK} l medali militer {LINK}</t>
+    <t>sp medali emas {LINK} putarrp medali emas {LINK} hidup medali emas {LINK} medali emas {LINK} mewah medali emas {LINK} sd medali emas {LINK} medali emas {LINK} st medali emas {LINK} menang rp medali militer {LINK} l medali militer {LINK}</t>
   </si>
   <si>
     <t>bosen x250 turun terus main kakek di situs 💦𝐄𝐑𝐀𝐉𝐏💦 u</t>
   </si>
   <si>
-    <t>bosan x turun main kakek situs keringat erajp keringat u</t>
+    <t>bosan x jatuh main kakek situs keringat erajp keringat u</t>
   </si>
   <si>
     <t>Seru abis! Setia banget sama ⭐💙𝐄𝐑𝐀𝐉𝐏💙⭐ sejak awal main ada aja ketujuan nya N</t>
   </si>
   <si>
-    <t>senang setia banget bintang medium putih hati biru erajp hati biru bintang medium putih main gol n</t>
+    <t>tarik setia banget bintang medium putih hati biru erajp hati biru bintang medium putih main gol n</t>
   </si>
   <si>
     <t>Emang gak ada yang se-mantep💦𝐄𝐑𝐀𝐉𝐏💦 deh. A</t>
   </si>
   <si>
-    <t>stabil keringat erajp keringat a</t>
+    <t>hebat a</t>
   </si>
   <si>
     <t>8180🎖️
@@ -1084,13 +1121,13 @@
     <t>Mantap emng ini situs gacor nya mantap MAHASLOT bener bener mantap abis WD 7jt bro #MAHASLOT</t>
   </si>
   <si>
-    <t>situs gacor mantap banget mahaslot mantap banget wd juta gan mahaslot</t>
+    <t>situs gacor bagus mahaslot mantap banget wd juta gan mahaslot</t>
   </si>
   <si>
     <t>PERHATIAN PERHATIAN !! 🌟𝐊𝗨𝐒𝗨𝐌𝗔𝐓𝟬𝐓𝟬🌟 BARU SUKSES WD 53jt MAXWIN hasil Buy SPin 1jt !!!! TERBUKTI TRUSTED WEB !!!</t>
   </si>
   <si>
-    <t>perhati perhati bintang sinar kusumatt bintang sinar sukses wd juta maxwin hasil beli spin juta website bukti percaya</t>
+    <t>perhati perhati bintang sinar kusumatt bintang sinar hasil wd juta hasil maxwin beli juta spin website bukti percaya</t>
   </si>
   <si>
     <t>Apa gak menyala kali hari INI ⭐𝐄𝐑𝐀𝐉𝐏⭐   i</t>
@@ -1108,7 +1145,7 @@
     <t>🌟🌟𝐊𝗨𝐒𝗨𝐌𝗔𝐓𝟬𝐓𝟬🌟🌟 yang lagi viral guys.. temanku bnyk yg CAIR dari sana. aku baru narek 2jt jg ..</t>
   </si>
   <si>
-    <t>bintang sinar bintang sinar kusumatt bintang sinar bintang sinar viral guys temenku hidup situ jt</t>
+    <t>bintang sinar bintang sinar kusumatt bintang sinar bintang sinar viral guys temenku jt</t>
   </si>
   <si>
     <t>Gokiil sih 𝐊𝗨𝐒𝗨𝐌𝗔𝐓𝟬𝐓𝟬 pantesan lagi viiral banget wkwkwk, saran aja buat yaang mau ikutan maiin jangan serakah kalau uda dapat 10x lipat dr moodal di wedeeh aja langsung kaya aku tadi, mataap polll 👍👍</t>
@@ -1138,37 +1175,37 @@
     <t>Hajar bang bo 𝗣𝗢𝗔𝟴𝟴 masih harum mahyongg2 nya sc nya harum bawa 50k dikaseh sgini kwkwk</t>
   </si>
   <si>
-    <t>hajar bang poa wangi mahyongg sc nya wangi bawa k kasih kwkwk</t>
+    <t>kalah gan poa wangi mahyongg sc nya wangi bawa k kasih kwkwk</t>
   </si>
   <si>
     <t>Dulu gw selalu rungkatt bang main di siitus lain, tapi kemarin lihat org komen main di 𝐊𝗨𝐒𝗨𝐌𝗔𝐓𝟬𝐓𝟬, akhirnya gw coba deepo 100rebo ga sampe 20menit saldoo gw meledak bang cair 4jt an wkwkwk</t>
   </si>
   <si>
-    <t>enggan main situs kemarin lihat komen main kusumatt coba deepo rebo menit saldo ledak gan cair juta hahaha</t>
+    <t>enggan main situs kemarin lihat orang komentar main kusumatt coba deepo rebo menit saldo ledak gan cair juta hahaha</t>
   </si>
   <si>
     <t>Nih bang gua saranin main di situs yang ngasih gua profit barusan bang, Mahyong PG sama Si Kakek Zeuuuussss lagi gacor bang. gua maen receh aja bang modal 100K, di 🌟𝐊𝗨𝐒𝗨𝐌𝗔𝐓𝟬𝐓𝟬🌟 ni bang mudah2an Dikasih Menang Depo pertama 🥰🥰Mantap💯</t>
   </si>
   <si>
-    <t>gan saran main situs untung gan mahjong pg bareng kakek zeus keren banget gan main uang receh gan modal k nih gan kasih menang deposit wajah senyum hati wajah senyum hati awesome nilai ratus</t>
+    <t>gan saran main situs untung gan mahjong tua gila banget gan ane main duit receh gan modal rb nih gan moga menang deposit wajah senyum hati wajah senyum hati mantap nilai ratus</t>
   </si>
   <si>
     <t>kalo pusing karna rungkad trs mending pindah ke #MAHASLOT di jamin JP gede'an</t>
   </si>
   <si>
-    <t>pusing gara gara galau mending pindah mahaslot jamin jp nya gede</t>
+    <t>pusing gara gara macet mending pindah mahaslot jamin gede</t>
   </si>
   <si>
     <t>Pemain 🔥🔥𝐊𝗨𝐒𝗨𝐌𝗔𝐓𝟬𝐓𝟬🔥🔥 kalau ditanya mau liburan ke mana, jawabnya apa? ( Ke angka-angka yang membawa keberuntungan! )</t>
   </si>
   <si>
-    <t>player api api kusumatt api api libur angka angka bawa untung</t>
+    <t>player api api kusumatt api api libur angka bawa untung</t>
   </si>
   <si>
     <t>kapan lagi bisa liat 🔥𝐊𝗨𝐒𝗨𝐌𝗔𝐓𝟬𝐓𝟬🔥 semenarik ini ya kan,, Tetap jadi yang terbaik dan jangan menyerah,, Wish 🔥𝐊𝗨𝐒𝗨𝐌𝗔𝐓𝟬𝐓𝟬🔥 tetap jadi yang terbaik di kelasnya</t>
   </si>
   <si>
-    <t>lihat api kusumatt api tarik ya serah wish api kusumatt api kelas</t>
+    <t>lihat api kusumatt api tarik serah wish api kusumatt api kelas</t>
   </si>
   <si>
     <t>member baru pun langsung pasti di 𝐄𝐑𝐀𝐉𝐏  kasih profit bang gua uda cobain l</t>
@@ -1180,7 +1217,7 @@
     <t>Gajian lebih awal makaasih rejeki nya ⭐𝐄𝐑𝐀𝐉𝐏⭐   k</t>
   </si>
   <si>
-    <t>gaji terima kasih rezeki bintang medium putih erajp bintang medium putih k</t>
+    <t>gaji terima kasih rejekinya bintang medium putih erajp bintang medium putih k</t>
   </si>
   <si>
     <t>Makasih "𝐏𝐈𝐂𝐊4𝐃"hutang gua bisa terbayar semua gara gara main di sini
@@ -1202,16 +1239,22 @@
     <t>senang kasih wd sibayar</t>
   </si>
   <si>
+    <t>Svip 2 20x depo nggk bisa naik emng apk babi</t>
+  </si>
+  <si>
+    <t>svip deposit x apk babi</t>
+  </si>
+  <si>
     <t>bagi kalian yg belom tau 🌟𝐊𝗨𝐒𝗨𝐌𝗔𝐓𝟬𝐓𝟬🌟 coba maen disana supaya tau web asli yg profesional fair itu gmn.🌟𝐊𝗨𝐒𝗨𝐌𝗔𝐓𝟬𝐓𝟬🌟 situs Terpercaya jd menurut gw paling aman kalo maen di web besar. Coba aja sendiri bang .</t>
   </si>
   <si>
-    <t>coba main website asli profesional adil bintang sinar kusumatt bintang sinar situs percaya aman main website coba kawan</t>
+    <t>coba main website asli profesional adil bintang sinar kusumatt bintang sinar situs percaya aman main website coba gan</t>
   </si>
   <si>
     <t>gak ada obat pola RTP dari 𝐊𝗨𝐒𝗨𝐌𝗔𝐓𝟬𝐓𝟬 di buat tembuss 4jt an dengan modal 90rb doangg sampai salto2 di kasurr wkwk 🤣🤣</t>
   </si>
   <si>
-    <t>obat pola rtp kusumatt capai juta modal ribu jungkir kasur hahaha tertawa bahak bahak tertawa bahak bahak</t>
+    <t>gak obat pola rtp kusumatt capai juta modal ribu laku flips kasur hahaha tertawa bahak bahak tertawa bahak bahak</t>
   </si>
   <si>
     <t>Eh cair" mantab kali emang ni ah ⭐𝐄𝐑𝐀𝐉𝐏⭐  M</t>
@@ -1239,7 +1282,7 @@
 LINK DAFTAR :https://www .pascaunhas .net/spanel/</t>
   </si>
   <si>
-    <t>ggsoft harvest anggota daftar ledak panen main modal rb jp juta link daftar {LINK} pascaunhas net spanel</t>
+    <t>ggsoft panen member daftar ledak panen main modal ribu langsung nyampe juta taut daftar {LINK} pascaunhas net spanel</t>
   </si>
   <si>
     <t>💈𝗘𝘃𝗲𝗻𝘁 𝗕𝗼𝗻𝘂𝘀 𝗦𝗰𝗣𝗴𝘀𝗼𝗳𝘁 𝗠𝗮𝗵𝗷𝗼𝗻𝗴𝟭&amp;𝟮 𝗣𝗼𝗼𝗹𝘀𝟯𝟬𝟯💈
@@ -1253,7 +1296,7 @@
 6. S&amp;K Berlaku Tidak Dapat diganggu gugat!</t>
   </si>
   <si>
-    <t>tanda salon event bonus scpgsoft mahjong pools tanda salon taut daftar {LINK} event wajib minimal deposit ribu laku deposit pulsa maksimal claim x userid max event bonus rb claim taruh pencar gabung event freespin buyspin hitung x klaim s k laku ganggu gugat</t>
+    <t>tanda salon event bonus scpgsoft mahjong pools tanda salon taut daftar {LINK} event deposit minimal ribu laku deposit pulsa maksimum klaim x userid bonus event maksimal ribu klaim taruh pencar gabung event freespin buyspin hitung x klaim s k batal</t>
   </si>
   <si>
     <t>emang joss banget niih 𝐊𝗨𝐒𝗨𝐌𝗔𝐓𝟬𝐓𝟬 ngasihh scaterr muluu, temen gw sampaii nanyain main dimana kok bisa scatter terus gw jawab main di 𝐊𝗨𝐒𝗨𝐌𝗔𝐓𝟬𝐓𝟬 , langsungg mabar bareng 👍</t>
@@ -1265,7 +1308,7 @@
     <t>Saran doang mas hajar 𝗣𝗢𝗔𝟴𝟴 gem uus1000nya meletup maswinnya</t>
   </si>
   <si>
-    <t>saran gan hajar poa permata uus nya ledak maswin nya</t>
+    <t>saran gan kalah poa permata uus nya ledak maswin nya</t>
   </si>
   <si>
     <t>Buset hoky benerr dah Setiap main di ⭐𝐄𝐑𝐀𝐉𝐏⭐  N</t>
@@ -1280,13 +1323,13 @@
 #aplikasipenghasiluang #gamepenghasiluang #slt138</t>
   </si>
   <si>
-    <t>uang sayap slt game ggsoft modal minimal jp uang sayap informasi {LINK} aplikasi hasil uang game hasil uang slt</t>
+    <t>uang sayap game slt seru banget ggsoft modal minimal langsung capai jp uang sayap info {LINK} aplikasi hasil uang game hasil uang slt</t>
   </si>
   <si>
     <t>Mari coba di 𝐊𝗨𝐒𝗨𝐌𝗔𝐓𝟬𝐓𝟬 dengan rate kemenangan ting1gi Perkalian Merah sering muncul</t>
   </si>
   <si>
-    <t>yuk coba kusumatt win rate multiplikasi merah muncul</t>
+    <t>yuk coba kusumatt win rate muncul kali merah</t>
   </si>
   <si>
     <t>17.06
@@ -1326,7 +1369,7 @@
     <t>Gampang WD bnget bro #MAHASLOT senggol dikit langsung jp mantap</t>
   </si>
   <si>
-    <t>gampang banget wdnya gan mahaslot senggol bagus</t>
+    <t>gampang banget wd gan mahaslot langsung nudge mantap</t>
   </si>
   <si>
     <t>lepas uang kereta awak main di 𝐃𝐨𝐢𝟴𝟴, keluar keluar kali merah nya we</t>
@@ -1356,7 +1399,7 @@
     <t>Nyenengin banget situs ⭐𝐄𝐑𝐀𝐉𝐏⭐ bray full senyum awak di buat nya P</t>
   </si>
   <si>
-    <t>situs seru banget bintang medium putih erajp bintang medium putih gan senyum penuh hasil p</t>
+    <t>seru banget situs bintang medium putih erajp bintang medium putih gan penuh senyum hasil</t>
   </si>
   <si>
     <t>Serius deh ⭐𝐄𝐑𝐀𝐉𝐏⭐ gk ngebosenin. Pln</t>
@@ -1380,7 +1423,7 @@
     <t>Gausah Ragu main di ⭐𝐄𝐑𝐀𝐉𝐏⭐ pasti gacorr abiss boskuh 💯💯 O</t>
   </si>
   <si>
-    <t>ragu main bintang medium putih erajp bintang medium putih gacorr abiss bosskuh nilai ratus nilai ratus o</t>
+    <t>sungkan main bintang medium putih erajp bintang medium putih gamenya bagus bos nilai ratus nilai ratus o</t>
   </si>
   <si>
     <t>👑NEW PROVIDER GGSOFT #SLT138
@@ -1390,7 +1433,7 @@
 LINK DAFTAR :https://www .exhalenevada .com/press</t>
   </si>
   <si>
-    <t>mahkota sedia ggsoft slt api acara khusus ggsoft bonus multiplikasi fantastis tabrak main mudah slt link daftar {LINK} exhalenevada com press</t>
+    <t>mahkota sedia ggsoft slt api acara khusus ggsoft bonus kelipat fantastis tabrak main uang mudah slt taut daftar {LINK} exhalenevada com press</t>
   </si>
   <si>
     <t>Gue lebih sering hoki di 𝐆𝐔𝐍𝐔𝐍𝐆𝟏𝟔𝟗 mode manual daripada auto. Kalian gimana?</t>
@@ -1420,13 +1463,13 @@
     <t>Nyenengin banget situs ⭐𝐄𝐑𝐀𝐉𝐏⭐ bray full senyum awak di buat nya O</t>
   </si>
   <si>
-    <t>situs seru banget bintang medium putih erajp bintang medium putih gan senyum penuh hasil o</t>
+    <t>situs senang bintang medium putih erajp bintang medium putih kawan senyum penuh hasil o</t>
   </si>
   <si>
     <t>Hajar bang bo 𝗣𝗢𝗔𝟴𝟴 masih harum mahyongg2 nya sc nya harum bawa 50k dikaseh 2 jtaan kwkwk</t>
   </si>
   <si>
-    <t>beat it bro poa wangi mahyongg sc nya wangi bawa k kasih juta kwkwk</t>
+    <t>kalah gan poa wangi mahyongg sc nya wangi bawa k kasih juta kwkwk</t>
   </si>
   <si>
     <t>16.06
@@ -1442,13 +1485,13 @@
     <t>member baru pun langsung pasti di 𝐄𝐑𝐀𝐉𝐏  kasih profit bang gua uda cobain T</t>
   </si>
   <si>
-    <t>member erajp untung gan coba t</t>
+    <t>member langsung erajp ngasih untung gan udah coba</t>
   </si>
   <si>
     <t>Main di SitusOKEBET303 udah pasti cuan ngab, gua udah nyobain beneran dikasi propit</t>
   </si>
   <si>
-    <t>main situs okebet uang udah coba banget kasih untung</t>
+    <t>main situsokebet uang udah coba banget kasih untung</t>
   </si>
   <si>
     <t>Kontroversi</t>
@@ -1466,7 +1509,7 @@
     <t>Gemoy</t>
   </si>
   <si>
-    <t>permata</t>
+    <t>gemoy</t>
   </si>
   <si>
     <t>Pisang goreng</t>
@@ -1482,9 +1525,6 @@
   </si>
   <si>
     <t>Duit truuus</t>
-  </si>
-  <si>
-    <t>uang sulit</t>
   </si>
   <si>
     <t>Coba ini
@@ -1512,7 +1552,7 @@
     <t>Emang gak ada yang se-mantep💦𝐄𝐑𝐀𝐉𝐏💦 deh. r</t>
   </si>
   <si>
-    <t>stabil keringat erajp keringat r</t>
+    <t>hebat r</t>
   </si>
   <si>
     <t>bosen x250 turun terus main kakek di situs 💦𝐄𝐑𝐀𝐉𝐏💦 P</t>
@@ -1524,7 +1564,7 @@
     <t>Aplikasi sedot WC,,, 6SVIP NEW APK 777</t>
   </si>
   <si>
-    <t>aplikasi sedot wc svip new apk</t>
+    <t>aplikasi sedot toilet svip new apk</t>
   </si>
   <si>
     <t>bangkai semua tu boskuuu</t>
@@ -1549,7 +1589,7 @@
     <t>Game lonte</t>
   </si>
   <si>
-    <t>main jalang</t>
+    <t>main nakal</t>
   </si>
   <si>
     <t>Apk anjing</t>
@@ -1564,6 +1604,12 @@
     <t>wd bos juta mahaslot gacor</t>
   </si>
   <si>
+    <t>apk keregak bisa wd</t>
+  </si>
+  <si>
+    <t>apk wd</t>
+  </si>
+  <si>
     <t>𝑺𝜮𝜟 𝜞𝑪𝜢 𝑮𝜣𝜣𝑮𝑳𝜮: ⚜⚜ S=U=P=E=R=C=U=A=N=8=8 ⚜⚜</t>
   </si>
   <si>
@@ -1573,7 +1619,7 @@
     <t>⚜𝐒𝐔𝐏𝐄𝐑𝐂𝐔𝐀𝐍𝟖𝟖 ⚜Hidup tak seindah drama Korea yang biasa kau tonton, tapi juga tak setragis sinetron azab, ini cuma permainan ringan. Asal jgn tamak bisa profit kok tapi maennya di ⚜𝐒𝐔𝐏𝐄𝐑𝐂𝐔𝐀𝐍𝟖𝟖 ⚜ ya</t>
   </si>
   <si>
-    <t>fleur de lis supercuan fleur de lis hidup indah drama korea tonton parah sinetron kiamat main ringan serakah untung main fleur de lis supercuan fleur de lis</t>
+    <t>fleur de lis supercuan fleur de lis hidup indah drama korea tonton parah sinetron kiamat main ringan serakah untung main fleur de lis supercuan fleur de lis ok</t>
   </si>
   <si>
     <t>Keren Banget 📌 𝐒𝐔𝐏𝐄𝐑𝐂𝐔𝐀𝐍𝟖𝟖📌</t>
@@ -1604,7 +1650,7 @@
 #KINGHOKI4D #SLOTGACOR #RTPLIVE</t>
   </si>
   <si>
-    <t>kinghokid ledak fragmen bossku wanita tari wanita tari wanita tari kinghokid slotgacor rtplive</t>
+    <t>kinghokid ledak pecah bossku wanita tari wanita tari wanita tari kinghokid slotgacor rtplive</t>
   </si>
   <si>
     <t>Cinta tak selalu penuh tawa, tapi tetap setia di tengah air mata</t>
@@ -1616,7 +1662,7 @@
     <t>Termangu hatiku</t>
   </si>
   <si>
-    <t>hati cengang</t>
+    <t>hati hilang</t>
   </si>
   <si>
     <t>💜💜𝐋𝐚𝐠𝐢 𝐋𝐚𝐮𝐧𝐜𝐡𝐢𝐧𝐠,,, 𝐏𝐫𝐨𝐦𝐨 𝐁𝐮𝐚𝐭 𝐌𝐞𝐦𝐛𝐞𝐫 𝐁𝐚𝐫𝐮,,, 𝐃𝐢𝐣𝐚𝐦𝐢𝐧 𝐖𝐃,,, 𝐔𝐝𝐡 𝐒𝐚𝐲𝐚 𝐑𝐚𝐬𝐚𝐢𝐧 𝐒𝐞𝐧𝐝𝐢𝐫𝐢👍🔥💜น่ารักมากเลยค่ะ🔥💜ขอบคุณมากนะคะ🔥💜おめでと-うございます🔥🔥🔥🎉💜💜💜💜💜💜💜💜💜🅲🅻🅸🅲🅺➤
@@ -1643,13 +1689,13 @@
     <t>Super Mantap#𝗟𝗔𝗞𝗘𝗥𝗦𝟰𝗗</t>
   </si>
   <si>
-    <t>lakersd</t>
+    <t>hebat lakersd</t>
   </si>
   <si>
     <t>sudah banyak ku main di situs lain yang ada di komentar ini Yang paling jelas ya  𝗚.𝗘.𝗥.𝗔.𝗜.𝗧.𝗢.𝗚.𝗘.𝗟  aja cok terbaik pokonya Menang pasti bayar sampai tuntas!!! Tanpa basa basi gak kek web lain menang dikit di blokir hehehe</t>
   </si>
   <si>
-    <t>main situs komentar g e r a i t o g e l pokok pokok menang bayar lunas basa basi website blokir hehehe</t>
+    <t>main situs komentar g e r a i t o g e l pokok pokok menang bayar selesai basa basi website blokir hehehe</t>
   </si>
   <si>
     <t>🤣🤣🤣𝗪𝗔𝗝𝗜𝗕 𝗖𝗢𝗕𝗔 𝗗𝗜 𝗦𝗜𝗡𝗜 𝗕𝗢𝗦 
@@ -1657,7 +1703,7 @@
 👍 GG SUPER TERBARU INI LINK,TERBARU PALING AMAN DAN TERPECAYA DENGAN RTP ATAS 98%🌹🌹🌹🌹🌹🌹🌹🌹🌹🌹🌹🌹🌹              https://heylink.me/SERVER.AUSTRALIA.RESMI.SDY77PRO                                                                        𝗪𝗜𝗡𝗧𝗔𝗥𝗘 𝗠𝗘𝗠𝗕𝗘𝗥 𝗕𝗔𝗥𝗨 𝟵𝟵% BAGUS BANGET SEMOGA REJEKINYA NULAR BOS</t>
   </si>
   <si>
-    <t>tertawa bahak bahak tertawa bahak bahak tertawa bahak bahak wajib coba bos super hati no thailand jempol link super gg aman percaya rtp mawar mawar mawar mawar mawar mawar mawar mawar mawar mawar mawar mawar mawar {LINK} wf</t>
+    <t>tertawa bahak bahak tertawa bahak bahak tertawa bahak bahak wajib coba bos super hati no thailand jempol link gg super ram percaya rtp mawar mawar mawar mawar mawar mawar mawar mawar mawar mawar mawar mawar mawar {LINK} wintare member bagus banget moga rezeki tular bos</t>
   </si>
   <si>
     <t>🧘‍♂️ Hati tenang, rezeki pun lancar. Karena kamu main di HMD29.</t>
@@ -1672,7 +1718,7 @@
 𝗪𝗜𝗡𝗧𝗔𝗥𝗘_𝗠𝗘𝗠𝗕𝗘𝗥 𝗕𝗔𝗥𝗨 𝟵𝟵% SEMOGA REJEKINYA NULAR BOS 🥳</t>
   </si>
   <si>
-    <t>super takjub hati merah pgsoft sensasional olympus same princes jempol wajah cium hebat indah bos q medali militer medali militer medali militer medali militer medali militer medali militer medali militer medali militer {LINK} kh hati kh hati kh hati kh hati thai hati thai winwp</t>
+    <t>super hebat hati merah sensasi pgsoft olympus pangeran jempol wajah cium hebat indah bos q medali militer medali militer medali militer medali militer medali militer medali militer medali militer medali militer {LINK} kh hati kh hati kh hati kh hati thai hati thai wintare member wajah pesta</t>
   </si>
   <si>
     <t>Pembohong</t>
@@ -1696,13 +1742,13 @@
     <t>Saldo GK mampu naik</t>
   </si>
   <si>
-    <t>saldo gk</t>
+    <t>saldo</t>
   </si>
   <si>
     <t>Hoax gd bonus nya</t>
   </si>
   <si>
-    <t>hoax bonus</t>
+    <t>bonus tipu</t>
   </si>
   <si>
     <t>UPDATE TERBARU 👇👇
@@ -1714,7 +1760,7 @@
 ==&gt;https://superboy.me/spin777&lt;==</t>
   </si>
   <si>
-    <t>update taut unduh apk {LINK} taut daftar {LINK}</t>
+    <t>taut unduh apk {LINK} taut daftar {LINK}</t>
   </si>
   <si>
     <t>link nya mana bos</t>
@@ -1738,7 +1784,7 @@
     <t>Rekomendasi dari kawan gua asli gacornya guys #MAHASLOT</t>
   </si>
   <si>
-    <t>rekomendasi temen temen asli gacor guys mahaslot</t>
+    <t>rekomendasi sobat asli gacor guys mahaslot</t>
   </si>
   <si>
     <t>YANG INI KAK PASTI WD , 𝘭𝘪𝘯𝘬𝘯𝘺𝘢 𝘣𝘪𝘴𝘢 𝘬𝘦𝘵𝘪𝘬 𝘥𝘪 𝘨𝘰𝘰𝘨𝘭𝘦 : 🔍 𝐋𝐄𝐕𝐈𝐒𝐓𝟎𝐓𝟎</t>
@@ -1768,31 +1814,37 @@
     <t>Bahagianya player itu sederhana,pecah perkalian aja pas main,ga perlu di ragukan lagi,apalagi mainnya di WEB ini #DAGELAN4D,,situs online terpercaya dan terlengkap,udah pasti aman brayy</t>
   </si>
   <si>
-    <t>gembira main sederhana selesai kali main ragu main web dageland situs online lengkap percaya aman gan</t>
+    <t>bahagia playernya sederhana pecah kali main ragu main website dageland situs online percaya lengkap aman gan</t>
   </si>
   <si>
     <t>Transaksi aman, saldo nambah terus, dan WeDeeh pun mulus. 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢 memang situs yang bisa diandalkan, 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢 TERBAIK DAH !!!</t>
   </si>
   <si>
-    <t>transaksi aman saldo wedeeh lancar bazartoto situs percaya bazartoto the best bye</t>
+    <t>transaksi aman saldo wedeeh lancar bazartoto situs percaya bazartoto</t>
   </si>
   <si>
     <t>Kemarin aku pecah rekor bang, main di 𝐁𝐀𝐙𝐀𝐑𝐓𝐎𝐓𝐎 modal 100reboo doang wedeh ku tembus 8jt-an aku main mahyong2 sama wild banditoo gokilll wkwkkwk🤣🤣</t>
   </si>
   <si>
-    <t>kemarin pecah rekor gan main bazartoto modal reboo juta main mahjong banditoo liar gokil hahaha tertawa bahak bahak tertawa bahak bahak</t>
+    <t>kemarin pecah rekor gan main bazartoto modal reboo juta main mahjong banditoo liar gokill hahaha tertawa bahak bahak tertawa bahak bahak</t>
   </si>
   <si>
     <t>Makasih yah bang uda kenalin 𝐁𝐀𝐙𝐀𝐑𝐓𝐎𝐓𝐎, gw td depo modal 50rb bs wd 870rb beneran ga nyangka 🥰</t>
   </si>
   <si>
-    <t>terima kasih gan kasih info bazartoto modal deposit rb wd rb gak nyangka banget wajah senyum hati</t>
+    <t>makasih gan udh kasih info bazartoto modal setor rb wd rb gak nyangka banget wajah senyum hati</t>
   </si>
   <si>
     <t>Tadinya ku kira boongan, tapi setelah di coba sendiri sekarang baru percaya nyepiin di 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢 emang lebiih gampang kena coy, aku sama kawan2ku pd wedeeh semua hari ini 👍👍</t>
   </si>
   <si>
     <t>bohong coba tipu mudah teman teman wedeeh jempol jempol</t>
+  </si>
+  <si>
+    <t>𝐌𝐚𝐤𝐢𝐧 𝐡𝐚𝐫𝐢 𝐦𝐚𝐤𝐢𝐧 𝐠𝐚𝐜𝐨𝐫 𝐚𝐣𝐚 𝐌𝐚𝐢𝐧 𝐃𝐢𝐬𝐢𝐧𝐢...</t>
+  </si>
+  <si>
+    <t>gacor main</t>
   </si>
   <si>
     <t>Baru coba Starlight Princess di 𝐒𝐔𝐏𝐄𝐑𝐂𝐔𝐀𝐍𝟖𝟖, langsung menang banyak dong 🍀</t>
@@ -1837,10 +1889,28 @@
     <t>slot gacr arah kanan ramatogel slot gacr arah kanan ramatogel slot gacr arah kanan ramatogel slot gacr arah kanan ramatogel slot gacr arah kanan ramatogel</t>
   </si>
   <si>
+    <t>Slot TT789 / SM605 / 8055 / H03 apk game bosok di promosikan</t>
+  </si>
+  <si>
+    <t>slot tt sm h apk game bosok promosi</t>
+  </si>
+  <si>
+    <t>Slot TT789 / SM605 / 8055 / H03 apk paling anjing bangke rongsokan</t>
+  </si>
+  <si>
+    <t>slot tt sm h apk anjing bangke rongkok</t>
+  </si>
+  <si>
+    <t>Slot TT789 / SM605 / 8055 / H03 situs gk bisa wd...hanya depo aja ...situs penipu jangan coba2x ....beritahu member lain</t>
+  </si>
+  <si>
+    <t>situs slot tt sm h draw deposit situs tipu coba coba member</t>
+  </si>
+  <si>
     <t>New member dimanjain banget guys di #MAHASLOT</t>
   </si>
   <si>
-    <t>member manja banget nih guys mahaslot</t>
+    <t>member manja banget guys mahaslot</t>
   </si>
   <si>
     <t>🍉🍉🍉🍉🍉🍉🍉🍉 SUPER MANTAP❤️,rasakan sendiri SENSASIONAL PGSOFT, OLYMPUS SAMA PRINCES &amp; Lainnya 👍😘 mantap berbagi itu indah boss q
@@ -1849,7 +1919,7 @@
 𝗪𝗜𝗡𝗧𝗔𝗥𝗘_𝗠𝗘𝗠𝗕𝗘𝗥 𝗕𝗔𝗥𝗨 𝟵𝟵% SEMOGA REJEKINYA NULAR BOS 🥳</t>
   </si>
   <si>
-    <t>semangka semangka semangka semangka semangka semangka semangka semangka super stunning hati merah pgsoft sensasional olympus princes jempol wajah cium mantap sharingnya cantik boss q link untung api nilai ratus winwp</t>
+    <t>semangka semangka semangka semangka semangka semangka semangka semangka super mantap hati merah sensasi pgsoft olympus pangeran jempol wajah cium hebat indah bos q link untung api nilai ratus wintare member wajah pesta</t>
   </si>
   <si>
     <t>Semoga sukses</t>
@@ -1863,7 +1933,7 @@
 https://hylink.pro/Slot-Indonesia</t>
   </si>
   <si>
-    <t>coba main ikland layan live chatnya ramah maxwin wd asik main {LINK}</t>
+    <t>coba main add layan live chatnya ramah maxwin wd keren main {LINK}</t>
   </si>
   <si>
     <t>HANYA DISINI JELAS TEPERCAYA JAMINAN PROFIT !! ❤️❤️🔥𝐆 𝐄 𝐑 𝐀 𝐈 𝐓 𝟎 𝐆 𝐄 𝐋🔥❤️❤️</t>
@@ -1883,13 +1953,25 @@
 ���10Xauto����5Xmanual ���20Xauto����10Xauto DC,, semoga gacor�#pg&amp;pragmatic</t>
   </si>
   <si>
-    <t>wajah cium mata tutup wajah cium mata tutup wajah cium mata tutup mahkota mahkota mahkota mahkota mahkota mahkota mahkota mahkota mahkota super mantap link stabil pelangi pelangi pelangi rtp no asia bagus selamat untung bosqu api marah yin daftar id pro c l i c k link {LINK} lampu lintas horizontal lampu lintas horizontal lampu lintas horizontal lampu lintas horizontal lampu lintas horizontal lampu lintas horizontal lampu lintas horizontal lampu lintas horizontal lampu lintas horizontal xautoxmanual xautoxauto dc moga hasil pg pragmatic</t>
+    <t>wajah cium mata tutup wajah cium mata tutup wajah cium mata tutup mahkota mahkota mahkota mahkota mahkota mahkota mahkota mahkota mahkota super mantap link stabil pelangi pelangi pelangi rtp no asia bagus banget moga sukses bosqu api marah yin daftar id pro c l i c k link {LINK} lampu lintas horizontal lampu lintas horizontal lampu lintas horizontal lampu lintas horizontal lampu lintas horizontal lampu lintas horizontal lampu lintas horizontal lampu lintas horizontal lampu lintas horizontal xautoxmanual xautoxauto dc moga work pg pragmatic</t>
   </si>
   <si>
     <t>Ga nyesel ikutin saran temen untuk main di situs ini,Alhasil gua menang besar juga makasi 𝐀𝐑𝐀𝐇𝟒𝐃 https://linky.wiki/Cuan-Gampang/</t>
   </si>
   <si>
-    <t>sesal saran teman main situs hasil menang terima kasih arahd {LINK}</t>
+    <t>sesal saran teman main situs alhasil menang terima kasih arahd {LINK}</t>
+  </si>
+  <si>
+    <t>Rahmanawati ini</t>
+  </si>
+  <si>
+    <t>rahmanawati</t>
+  </si>
+  <si>
+    <t>Sepeserpun gak pernah naik</t>
+  </si>
+  <si>
+    <t>sen</t>
   </si>
   <si>
     <t>Awas sedot wc</t>
@@ -1898,17 +1980,41 @@
     <t>hati hati hisapan toilet</t>
   </si>
   <si>
+    <t>Kode bonus</t>
+  </si>
+  <si>
+    <t>kode bonus</t>
+  </si>
+  <si>
+    <t>Situss busuk cuma terima depo ST789 APK 9.9 - Unduh Versi Terbaru</t>
+  </si>
+  <si>
+    <t>situs busuk terima st deposit apk unduh versi</t>
+  </si>
+  <si>
     <t>Nani Minarni blm bisa</t>
   </si>
   <si>
     <t>nan minarni laku</t>
+  </si>
+  <si>
+    <t>Apk terlaknak babi anjing</t>
+  </si>
+  <si>
+    <t>apk anjing babi terlaknak</t>
+  </si>
+  <si>
+    <t>Irpansi Irpan super lengkap</t>
+  </si>
+  <si>
+    <t>irpansi irpan super lengkap</t>
   </si>
   <si>
     <t>SUPER BAIK 👑𝐏𝐋𝐀𝐘𝟐𝟐𝐏𝐆👑 SUKSES SELALU AMINSUPER SUPER GACOR #𝐏𝐋𝐀𝐘𝟐𝟐𝐏𝐆 SEMAKIN SUKSES AMIN super mantap #𝐏𝐋𝐀𝐘𝟐𝟐𝐏𝐆, terbaik bagus banget semoga aja bisa nular sm pelayer laenSuper Bagus 𝐏𝐋𝐀𝐘𝟐𝟐𝐏𝐆💎
 Super Bagus 𝐏𝐋𝐀𝐘𝟐𝟐𝐏𝐆💎SUPER BAGUS                       𝐏𝐋𝐀𝐘𝟐𝟐𝐏𝐆                                                              SEMOGA REJEKINYA NULAR BOSSUPER SUPER GACOR #𝐏𝐋𝐀𝐘𝟐𝟐𝐏𝐆 SEMAKIN SUKSES AMIN</t>
   </si>
   <si>
-    <t>super mahkota playpg mahkota sukses aminsuper super gacor playpg sukses amin super hebat playpg bagus banget moga tular main bagus playpg batu permata bagus banget playpg sukses amin</t>
+    <t>super bagus mahkota playpg mahkota sukses aminsuper super gacor playpg sukses amin super hebat playpg bagus banget moga tular main laen super jago playpg batu permata super bagus playpg batu permata super bagus playpg sukses amin</t>
   </si>
   <si>
     <t>Spin889 dulu pernah narik disitu</t>
@@ -1921,25 +2027,37 @@
   </si>
   <si>
     <t>rejeki anak shaleh kamsia tegang tarung tegang</t>
+  </si>
+  <si>
+    <t>Situs rungkad #raya4D</t>
+  </si>
+  <si>
+    <t>situs rungkad rayad</t>
+  </si>
+  <si>
+    <t>sedot WC 8 x deposit new member tanpa WD, hati hati aja</t>
+  </si>
+  <si>
+    <t>sedot wc x deposit member wc hati hati</t>
   </si>
   <si>
     <t>Ini baru jujur bos .yakin lah mudah mudahan.wd bos..saya modal.20k.dikasi.450k.
  Depo lagi saya 30k.dikasih lagi 500k.haei ini saya baru main apk ini.apk lain sampah semua nya.penipu...</t>
   </si>
   <si>
-    <t>dar jujur bos harap wd bos modal k dik k laku deposit rb k hai main apk apk sampah tipu</t>
+    <t>dar jujur bos harap wd bos modal k didik k laku deposit rb k hai main apk apk sampah tipu</t>
   </si>
   <si>
     <t>Tadi iseng coba ikutin saran teman gw main di 𝐁𝐀𝐙𝐀𝐑𝐓𝐎𝐓𝐎 ternyata beneran di kasih Jipi wkwk, makasih bro 😜</t>
   </si>
   <si>
-    <t>coba saran teman main bazartoto nyata jip beneran ngasih haha makasih gan wajah julur lidah kedip mata</t>
+    <t>iseng coba saran teman main bazartoto nyata jeep terima kasih gan wajah julur lidah kedip mata</t>
   </si>
   <si>
     <t>Gokiil sih 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢 pantesan lagi viiral banget wkwkwk, saran aja buat yaang mau ikutan maiin jangan serakah kalau uda dapat 10x lipat dr moodal di wedeeh aja langsung kaya aku tadi, mataap polll 👍👍</t>
   </si>
   <si>
-    <t>gila banget bazartoto viral hahaha saran main serakah uang x wedeeh langsung kaya mataap pol jempol jempol</t>
+    <t>gila bazartoto pantes viral hahaha dar saran main serakah uang x wedeeh langsung kaya mataap pol jempol jempol</t>
   </si>
   <si>
     <t>cintai di 𝐒𝐔𝐏𝐄𝐑𝐂𝐔𝐀𝐍𝟖𝟖 bonus nya gak main main,𝐒𝐔𝐏𝐄𝐑𝐂𝐔𝐀𝐍𝟖𝟖 selalu ada kejutan yang menarik</t>
@@ -1963,7 +2081,7 @@
     <t>Main santai di 𝐒𝐔𝐏𝐄𝐑𝐂𝐔𝐀𝐍𝟖𝟖, eh slot Sweet Bonanza kasih maxwin! 💰</t>
   </si>
   <si>
-    <t>main santai supercuan eh slot sweet bonanza suka maxwin kantung uang</t>
+    <t>main santai supercuan eh sweet bonanza slot love maxwin kantung uang</t>
   </si>
   <si>
     <t>🌟𝗦𝗜𝗗𝗢𝟴𝟴🌟 udah temenku  kerja di perusahaan itu. TRUSTED</t>
@@ -1994,7 +2112,7 @@
 ketik di google 𝗙𝗔𝗧4𝗗</t>
   </si>
   <si>
-    <t>bagus banget ragu kesini ketik google fatd</t>
+    <t>enak ragu kesini ketik google fatd</t>
   </si>
   <si>
     <t>Up</t>
@@ -2003,7 +2121,7 @@
     <t>Itu bos saya sudah capek Rungkat terus.ini apk jujur...</t>
   </si>
   <si>
-    <t>bos capek rungkat apk jujur</t>
+    <t>bos capek nulis apk jujur</t>
   </si>
   <si>
     <t>Baru saya main.dikasih.450k.saya depo 20k..hari ini...</t>
@@ -2015,13 +2133,19 @@
     <t>Itu bos hari ini aja...</t>
   </si>
   <si>
-    <t>sekian bos</t>
+    <t>bos</t>
+  </si>
+  <si>
+    <t>Dw saya ..</t>
+  </si>
+  <si>
+    <t>aduh</t>
   </si>
   <si>
     <t>Bagi link nya donk</t>
   </si>
   <si>
-    <t>sila taut</t>
+    <t>tolong taut</t>
   </si>
   <si>
     <t>Baru liris</t>
@@ -2042,10 +2166,16 @@
     <t>apk kontol</t>
   </si>
   <si>
+    <t>SDTWC</t>
+  </si>
+  <si>
+    <t>tspwc</t>
+  </si>
+  <si>
     <t>Apk situs miskin jangan mau main disini.</t>
   </si>
   <si>
-    <t>situs malang apk main</t>
+    <t>apk situs malang main</t>
   </si>
   <si>
     <t>Tolong bikin aplikasi game</t>
@@ -2064,6 +2194,12 @@
   </si>
   <si>
     <t>uwek uwek bos gaskaann</t>
+  </si>
+  <si>
+    <t>Ili Fitra Hayani mantappp</t>
+  </si>
+  <si>
+    <t>ili fitra hayani</t>
   </si>
   <si>
     <t>Apk Slot Online Nolimit https://2dsewskdf6sdesg.checkviasecureaccessynzdyndyyltgpy.com?code=DUKBWW1PZ5M&amp;t=1746966060</t>
@@ -2094,13 +2230,13 @@
     <t>SUPER MANTAP  ❤️‍🔥👉 𝗕𝗜𝗡𝗧𝗔𝗡𝗚𝗕𝗘𝗧𝟵𝟵🔥</t>
   </si>
   <si>
-    <t>hebat hati rap api arah kanan bintangbet api</t>
+    <t>super hebat hati rap api arah kanan bintangbet api</t>
   </si>
   <si>
     <t>SUPER HEBAT #𝗕𝗔𝗡𝗝𝗜𝗥𝗝𝗣𝟱𝟱🔥</t>
   </si>
   <si>
-    <t>hebat banjirjp api</t>
+    <t>super hebat banjirjp api</t>
   </si>
   <si>
     <t>𝗖𝗔𝗥𝗜 𝗔𝗝𝗔 𝗗𝗜 𝗚𝗢𝗢𝗚𝗟𝗘
@@ -2111,13 +2247,13 @@
 🍀🍀おめでとうござい🍀ส้มรักพ่อนะคะ พ่อก็รักส้มคMantap Congratulations หนุ่มพลังม้ Congratulations Threads 🧡 สุดปัง 🍊ฟ้ารักพ่อนะคะ Congratulations 🎀น่ารักมากเลยค่ะ🎀ขอบคุณมากนะ</t>
   </si>
   <si>
-    <t>cari aja google banjirjp mawar kilau daun tiup angin miiae dminduuael tl d chm hati ungu kh bkhunmaaknakha pita selamat selamat</t>
+    <t>cari aja google banjirjp mawar kilau daun tiup angin miiae dminduuael tl d chm hati ungu kh bkhunmaaknakha pita selamat selamat thread hati oranye sudpang buah jeruk faarakph nakha selamat pita naarakmaakelykha pita kh bkhunmaakna</t>
   </si>
   <si>
     <t>𝗖𝗢𝗕𝗔 𝗗𝗜 𝗦𝗜𝗡𝗜 𝗕𝗢𝗦 👍 SUPER MANTAP LINK PALING MANTAP 👍  https://heylink.me/SERVER.AUSTRALIA.RESMI.SDY77PRO  ✧ ▬▭▬ ▬▭▬ ✦✧𝗪𝗜𝗡𝗧𝗔𝗥𝗘_𝗠𝗘𝗠𝗕𝗘𝗥 𝗕𝗔𝗥𝗨 𝟵𝟵% 🅑🅞🅝🅤🅢 🅝🅔🅦 🅜🅔🅜🅑🅔🅡👍✦🌈🔥🌈พลัง Congratulations ดีมากคะ หนุ่มผมยาว</t>
   </si>
   <si>
-    <t>coba bhewan pelihara wintare member b o n u s n e w m e m b e r jempol pelangi api pelangi phlang selamat diimaakkha hnumphmyaaw</t>
+    <t>wintare member b o n u s n e w m e m b e r jempol pelangi api pelangi phlang selamat diimaakkha hnumphmyaaw</t>
   </si>
   <si>
     <t>Real dari Rusia
@@ -2136,7 +2272,7 @@
     <t>Gamenya seru, cuannya nyata! top markotop ⚡𝗣𝗲𝘁𝗮𝗿𝘂𝗻𝗴𝟭𝟯𝟴⚡</t>
   </si>
   <si>
-    <t>gamenya seru untung nyata markotop tegang tarung tegang</t>
+    <t>main senang untung nyata markotop tegang tarung tegang</t>
   </si>
   <si>
     <t>Makasi bng uda mau berbagi</t>
@@ -2154,13 +2290,13 @@
     <t>Sekali Tampil Harus Berhasil , Abis wd 8 jt di 🌟🌟𝗦𝗜𝗗𝗢𝟴𝟴🌟🌟 main kakek hehehe...</t>
   </si>
   <si>
-    <t>tampil sukses trus bayar juta bintang sinar bintang sinar sido bintang sinar bintang sinar main kakek hehehe</t>
+    <t>tampil sukses habis wd juta bintang sinar bintang sinar sido bintang sinar bintang sinar main kakek hehehe</t>
   </si>
   <si>
     <t>Gila tak masuk logika</t>
   </si>
   <si>
-    <t>gila masuk akal</t>
+    <t>gila logika</t>
   </si>
   <si>
     <t>🧲 𝗧𝗮𝗿𝗶𝗸𝗮𝗻 𝗵𝗼𝗸𝗶𝗻𝘆𝗮 𝗴𝗮𝗸 𝗺𝗮𝗶𝗻² 𝗕𝗢𝗦𝗤𝗨 — 𝗜𝗡𝗗𝗢𝗝𝗔𝗬𝗔𝟭𝟲𝟴!</t>
@@ -2190,25 +2326,25 @@
     <t>Dulu gw selalu rungkatt bang main di siitus lain, tapi kemarin lihat org komen main di 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢, akhirnya gw coba deepo 100rebo ga sampe 20menit saldoo gw meledak bang cair 4jt an wkwkwk</t>
   </si>
   <si>
-    <t>enggan main situs kemarin lihat orang komentar main bazartoto coba deepo rebo menit saldo ledak gan tunai juta hahaha</t>
+    <t>enggan main situs kemarin lihat komen main bazartoto coba deepo rebo menit saldo ledak gan juta cair hahaha</t>
   </si>
   <si>
     <t>Sekian banyak siitus yg gw mainin cuma 𝐁𝐀𝐙𝐀𝐑𝐓𝐎𝐓𝐎 yang paling ga pelit sketer, asli spin 20 kali pasti dapat sekali , kalau gini mah betah banget gw main disini 🤭🤭</t>
   </si>
   <si>
-    <t>situs main bazartoto pelit cepat spin kali betah banget main wajah tangan tutup mulut wajah tangan tutup mulut</t>
+    <t>sekian situs main bazartoto pelit skuter spin kali betah banget main wajah tangan tutup mulut wajah tangan tutup mulut</t>
   </si>
   <si>
     <t>Tadi malam iseng nyoba maiin di 𝐁𝐀𝐙𝐀𝐑𝐓𝐎𝐓𝐎, modal 40 rebo jadi 2jt-an kaget coyyy senang banget sampe ga bisa tidur wkwkwk</t>
   </si>
   <si>
-    <t>malam iseng coba main bazartoto modal rebo juta kaget banget neng banget sampe gak tidur hahaha</t>
+    <t>malam nyoba main bazartoto modal rebo juta kaget banget neng banget sampe gak tidur hahaha</t>
   </si>
   <si>
     <t>ALAH GAME MISKIN JANGAN DONWLOD</t>
   </si>
   <si>
-    <t>alah miskin game unduh</t>
+    <t>main buruk unduh</t>
   </si>
   <si>
     <t>Situs miskin</t>
@@ -2217,6 +2353,13 @@
     <t>situs buruk</t>
   </si>
   <si>
+    <t>Erwan Botek sama bg, begitu narik engk bisa malah di bilang 
+akun anda ilegal🤣🤣</t>
+  </si>
+  <si>
+    <t>erwan botek bg tarik bilang akun ilegal tertawa bahak bahak tertawa bahak bahak</t>
+  </si>
+  <si>
     <t>Erwan Botek</t>
   </si>
   <si>
@@ -2229,12 +2372,30 @@
     <t>nusa rhamadan coba bos</t>
   </si>
   <si>
+    <t>Hati hati sama aplikasi game ini hanya bikin sedot WC</t>
+  </si>
+  <si>
+    <t>hati hati aplikasi game toilet jelek</t>
+  </si>
+  <si>
     <t>Game murahan</t>
   </si>
   <si>
     <t>main murah</t>
   </si>
   <si>
+    <t>Kalah terus ga pernah d kasih menang</t>
+  </si>
+  <si>
+    <t>kalah menang</t>
+  </si>
+  <si>
+    <t>Situs bodong ga bisa wd</t>
+  </si>
+  <si>
+    <t>situs palsu wd</t>
+  </si>
+  <si>
     <t>Apa coba kek gini🤣🤣</t>
   </si>
   <si>
@@ -2245,6 +2406,12 @@
   </si>
   <si>
     <t>pandawa pandawa</t>
+  </si>
+  <si>
+    <t>Situs maling ini jangan ada yg mau</t>
+  </si>
+  <si>
+    <t>situs curi</t>
   </si>
   <si>
     <t>JACKPOT Terus Di Situs 𝐒𝐥𝐨𝐭𝐆𝐚𝐜𝐨𝐫 𝐙𝐨𝐨𝐦𝟓𝟓𝟓 RTP tertinggi
@@ -2254,13 +2421,16 @@
 ✔️ Bukti Jackpot  𝐙𝐨𝐨𝐦𝟓𝟓𝟓 https://zoom555jackpot.com/</t>
   </si>
   <si>
-    <t>jackpot situs slotgacor zoom rtp jackpot anggota langsung tanda centang tebal taut resmi zoom {LINK} tanda centang tebal link alternatif zoom {LINK} tanda centang tebal bukti jackpot zoom {LINK}</t>
+    <t>jackpot situs slotgacor zoom rtp jackpot anggota tanda centang tebal taut resmi zoom {LINK} tanda centang tebal link alternatif zoom {LINK} tanda centang tebal bukti jackpot zoom {LINK}</t>
   </si>
   <si>
     <t>PALING MANTAP #𝗥𝗔𝗝𝗔𝗪𝗘𝗕𝟭𝟴𝟳♨️🔥</t>
   </si>
   <si>
-    <t>takjub rajaweb sumber air panas api</t>
+    <t>rajaweb sumber air panas api</t>
+  </si>
+  <si>
+    <t>Situs maling</t>
   </si>
   <si>
     <t>👍🤫SUPER  MANTAP INI LINK,TERBAIK PALING MANTAP DENGAN RTP DI ATAS 98 🌟🌟🌟🌟⭐🌟🌟🌟🌟🌟🌟🌟🌟🌟⭐
@@ -2269,7 +2439,7 @@
 𝗪𝗜𝗡𝗧𝗔𝗥𝗘 𝗠𝗘𝗠𝗕𝗘𝗥 𝗕𝗔𝗥𝗨 𝟵𝟵% BAGUS BANGET SEMOGA AJA BISA NULAR SAMA PELAYER LAIN💖💖💖💖💖💖💖💖💖💖💖</t>
   </si>
   <si>
-    <t>jempol wajah suruh diam super negara link stabil rtp bintang sinar bintang sinar bintang sinar bintang sinar bintang medium putih bintang sinar bintang sinar bintang sinar bintang sinar bintang sinar bintang sinar bintang sinar bintang sinar bintang sinar bintang medium putih untung api nilai ratus wintare member harap buru main hati sinar hati sinar hati sinar hati sinar hati sinar hati sinar hati sinar hati sinar hati sinar hati sinar hati sinar</t>
+    <t>jempol wajah suruh diam bagus taut rtp bintang sinar bintang sinar bintang sinar bintang sinar bintang medium putih bintang sinar bintang sinar bintang sinar bintang sinar bintang sinar bintang sinar bintang sinar bintang sinar bintang sinar bintang medium putih untung api nilai ratus wintare member bagus banget moga tular main hati sinar hati sinar hati sinar hati sinar hati sinar hati sinar hati sinar hati sinar hati sinar hati sinar hati sinar</t>
   </si>
   <si>
     <t>🎰 Banyak pilihan pasaran resmi
@@ -2292,7 +2462,7 @@
     <t>Wede terus gw bree main di 𝐌𝐀𝐇𝐀𝐒𝐋𝐎𝐓</t>
   </si>
   <si>
-    <t>main mahaslot</t>
+    <t>wow main mahaslot</t>
   </si>
   <si>
     <t>Hoki bgt njir nyoba main di 𝐔𝐠𝟏𝟎𝟎 gacor pisan euy</t>
@@ -2310,20 +2480,20 @@
 NB: hapus tanda bintangnya (*) ya beb</t>
   </si>
   <si>
-    <t>batu permata intertogel togel pilih sultan tanda centang tebal setor minimum rendah tanda centang tebal diskon bonus tanda centang tebal support jam nonstop gabung raja dunia lotere mahkota {LINK} nb hilang tanda bintang gan</t>
+    <t>batu permata intertogel pilih sultan togel sejati tanda centang tebal setor minimum rendah tanda centang tebal diskon bonus tanda centang tebal dukung jam nonstop gabung raja dunia lotere mahkota {LINK} nb hilang tanda bintang gan</t>
   </si>
   <si>
     <t>Udah sering main di berbagai situs, tapi pola Mahjong di Preview Copy Tweet
 𝑴𝑼𝑫𝑰𝑲𝑺𝑳𝑶𝑻 paling sering kasih jackpot !!!</t>
   </si>
   <si>
-    <t>main situs pola mahjong pratinjau salin tweet mudikslot jackpot</t>
+    <t>main situs pola mahjong preview copy tweet mudikslot jackpot</t>
   </si>
   <si>
     <t>Serasa PRo kali yakan main nyaa...</t>
   </si>
   <si>
-    <t>pro main</t>
+    <t>orang profesional main</t>
   </si>
   <si>
     <t>Ayo, waktunya untuk memulai sesuatu yang baru!</t>
@@ -2335,19 +2505,19 @@
     <t>APK MISKIN TINGGALIN AJA</t>
   </si>
   <si>
-    <t>apk miskin tinggal</t>
+    <t>apk jelek biar</t>
   </si>
   <si>
     <t>gk usah pake2 pola, main di KRISNA96 cukup spin santai aja , langsung dikasih MENANG sampai WD</t>
   </si>
   <si>
-    <t>pakai pola main krisna spin santai langsung win wd</t>
+    <t>pola main krisna spin santai langsung menang</t>
   </si>
   <si>
     <t>Tangan panas banget hari ini! Trnyata wd beruntun 3x. thx ⚡𝗣𝗲𝘁𝗮𝗿𝘂𝗻𝗴𝟭𝟯𝟴⚡ 🔥</t>
   </si>
   <si>
-    <t>tangan sungguh panas nyata wd x terima kasih tegang tarung tegang api</t>
+    <t>tangan panas nyata wd kali terima kasih tegang tarung tegang api</t>
   </si>
   <si>
     <t>Feeling nggak pernah bohong! Skuy menang lagi! gacor abis ⚡𝗣𝗲𝘁𝗮𝗿𝘂𝗻𝗴𝟭𝟯𝟴⚡</t>
@@ -2371,7 +2541,7 @@
     <t>Aplikasi jancokkk kontol</t>
   </si>
   <si>
-    <t>aplikasi dick jancok</t>
+    <t>aplikasi kontol jancok</t>
   </si>
   <si>
     <t>Link bangsat</t>
@@ -2386,10 +2556,22 @@
     <t>main kontol ekor anjing</t>
   </si>
   <si>
+    <t>game anjing ini bro jangan main sama download nyesel main game sedot WC</t>
+  </si>
+  <si>
+    <t>gan main game anjing download sesal main game penghisap toilet</t>
+  </si>
+  <si>
+    <t>Gamee taii anjing jangan main disini</t>
+  </si>
+  <si>
+    <t>main game anjing taii</t>
+  </si>
+  <si>
     <t>Para admin kayak tai. Ikisitus.    Abal Abal</t>
   </si>
   <si>
-    <t>adminnya orang bodoh situs iki palsu</t>
+    <t>adminnya bodoh situs iki palsu</t>
   </si>
   <si>
     <t>Kalau soal gacooor, 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢 uda ga ada lawan guys. Makasi udah kasi gue menang terus 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢 !!!!!!</t>
@@ -2407,7 +2589,7 @@
     <t>Jalanin aja, nanti juga ngerti sendiri vibes-nya 𝗖𝗢𝗕𝗔 𝗗𝗜 𝗦𝗜𝗡𝗜 𝗕𝗨𝐊𝗧𝗜𝟰𝘿 👍  (WAJIB SAVE)</t>
   </si>
   <si>
-    <t>laku paham getar coba buktid jempol wajib hemat</t>
+    <t>laku paham getar coba buktid jempol wajib simpan</t>
   </si>
   <si>
     <t>Bacaan dan doa yang mulai berbeda</t>
@@ -2419,25 +2601,25 @@
     <t>🌟🌟𝗦𝗜𝗗𝗢𝟴𝟴🌟🌟 yang lagi viral guys.. temanku bnyk yg CAIR dari sana. aku baru narek 2jt jg ..</t>
   </si>
   <si>
-    <t>bintang sinar bintang sinar sido bintang sinar bintang sinar viral guys temenku hidup situ jt</t>
+    <t>bintang sinar bintang sinar sido bintang sinar bintang sinar viral guys temenku jt</t>
   </si>
   <si>
     <t>Link-nya udah di atas, tinggal gas aja 𝐒𝐔𝐏𝐄𝐑𝐂𝐔𝐀𝐍𝟖𝟖☃️Game-nya ringan, tapi cuannya bukan main 𝐒𝐔𝐏𝐄𝐑𝐂𝐔𝐀𝐍𝟖𝟖🌊</t>
   </si>
   <si>
-    <t>linknya gas supercuan boneka salju hujan salju main ringan untung supercuan ombak</t>
+    <t>linknya gas supercuan boneka salju hujan salju gamenya ringan untung nya gak supercuan ombak</t>
   </si>
   <si>
     <t>TERNYATA ini pusat penampungannya 🌟𝗦𝗜𝗗𝗢𝟴𝟴🌟 BD T0g3l Singapor3 semua masukknya disini nih 𝗦𝗜𝗗𝗢𝟴𝟴</t>
   </si>
   <si>
-    <t>nyata holding centernya bintang sinar sido bintang sinar bd tgl singapura kesini sido</t>
+    <t>nyata holding centernya bintang sinar sido bintang sinar bd tgl singapor kesini sido</t>
   </si>
   <si>
     <t>dulu nyoba2 main di 𝗣𝗢𝗡𝗦𝗘𝗟𝟲𝟵 modal 200rb dpet 16juta , langsung dibayar , nyoba di tempat lain malah rungkad apes emang ...ketik aja di google 𝗣𝗢𝗡𝗦𝗘𝗟𝟲𝟵</t>
   </si>
   <si>
-    <t>coba main ponsel modal rb jt langsung bayar coba petaka ketik google ponsel</t>
+    <t>coba main ponsel modal rb juta langsung bayar coba petaka ketik google ponsel</t>
   </si>
   <si>
     <t>fiman mantap</t>
@@ -2449,20 +2631,26 @@
     <t>Aku Wong Rak Ndue gas</t>
   </si>
   <si>
-    <t>rak ndue gas</t>
+    <t>orang hak isi bensin</t>
   </si>
   <si>
     <t>Gak perlu banyak basa basi kita lurr 😊 coba aja sendiri pundi pundi CUAN di ❤️𝑷𝑬𝑵𝑨𝑲𝑳𝑼𝑲𝑱𝑰𝑻𝑼❤️ gas🔥</t>
   </si>
   <si>
-    <t>basa basi yuk langsung coba cuan hati merah penaklukjitu hati merah gas api</t>
+    <t>basa basi yuk langsung coba raih rejeki hati merah penaklukjitu hati merah gas api</t>
   </si>
   <si>
     <t>TERBAIK PALING MANTAP DENGAN RTP DI ATAS 98%.
 LAGI BANYAK YANG JP MAXWIN DAN WD DI WEB SATU INI DENGAN 𝗪𝗜𝗡𝗧𝗔𝗥𝗘 𝗠𝗘𝗠𝗕𝗘𝗥 𝗕𝗔𝗥𝗨 𝟵𝟵% BAGUS BANGET SEMOGA AJA BISA NULAR SAMA PELAYER LAIN</t>
   </si>
   <si>
-    <t>stabil rtp jp maxwin wd website wintare member bagus harap nutar main</t>
+    <t>stabil rtp jp maxwin wd website wintare member bagus banget moga tular main</t>
+  </si>
+  <si>
+    <t>Janji gua mau membabi buta, buat nyebarin ini, judi slot bodo bodo &amp; ga ada yg kaya miskin miskin, klo ga mau d sebut miskin &amp; bodo bodo, jgn main judi slot,,</t>
+  </si>
+  <si>
+    <t>janji buta sebar judi slot bodoh kaya miskin miskin bodoh main judi slot</t>
   </si>
   <si>
     <t>Emang mantep banget #ARJUNA96, hari hari menang</t>
@@ -2501,7 +2689,13 @@
 ganti (,) pake (.)</t>
   </si>
   <si>
-    <t>class bree modal sia sia menang gan arjuna {LINK} ganti</t>
+    <t>kelas bree modal gak sia sia menang gan arjuna {LINK} ganti</t>
+  </si>
+  <si>
+    <t>Situs maling ini WD ga di proses</t>
+  </si>
+  <si>
+    <t>situs curi proses</t>
   </si>
   <si>
     <t>🌟𝐆.𝐄.𝐑.𝐀.𝐈.𝐓.𝐎.𝐆.𝐄.𝐋🌟 𝗱𝗲𝗽𝗼 𝗿𝗲𝗰𝗲𝗵 𝟮𝟬𝗿𝗯, 𝗪𝗗 𝘀𝗮𝗺𝗽𝗲 𝟲𝟮𝟬𝗿𝗯</t>
@@ -2550,25 +2744,25 @@
     <t>Lumayan buat isi waktu luang 𝐒𝐔𝐏𝐄𝐑𝐂𝐔𝐀𝐍𝟖𝟖🏕️Temen gue yang kenalin, sekarang gue yang nagih 𝐒𝐔𝐏𝐄𝐑𝐂𝐔𝐀𝐍𝟖𝟖💎</t>
   </si>
   <si>
-    <t>lumayan isi luang supercuan kemah teman kenal supercuan batu permata</t>
+    <t>lumayan isi luang supercuan batu permata</t>
   </si>
   <si>
     <t>Depohh receh main santai di 𝐁𝐀𝐙𝐀𝐑𝐓𝐎𝐓𝐎 asal jangan nafsu pasti wedeeh, apalagi kalau elu baru daftar pasti lebih di manjaiin dahh</t>
   </si>
   <si>
-    <t>depohh receh main santai bazartoto gak nafsu asik daftar manja</t>
+    <t>depohh receh main santai bazartoto gak serakah asik daftar manja</t>
   </si>
   <si>
     <t>gak ada obat pola RTP dari 𝗣𝟬𝗡𝗦𝗘𝗟𝟲𝟵 di buat tembuss 4jt an dengan modal 90rb doangg sampai salto2 di kasurr wkwk 🤣🤣</t>
   </si>
   <si>
-    <t>obat pola rtp pnsel tembus juta modal rb jungkir kasur hahaha tertawa bahak bahak tertawa bahak bahak</t>
+    <t>obat pola rtp pnsel tembus juta modal ribu jungkir kasur hahaha tertawa bahak bahak tertawa bahak bahak</t>
   </si>
   <si>
     <t>Nih saran aku aja ya bang, aku rekomenin kalian nyoba main di 𝐁𝐀𝐙𝐀𝐑𝐓𝐎𝐓𝐎 sana cocok bangeet buat pemula modal receeh sering di kasiih, asal jangan seraakah ku jamiin pastii bisa weedeh cobaiin deh</t>
   </si>
   <si>
-    <t>saran ane gan saran ane coba main bazartoto cocok banget modal cadang gak serakah ane jamin coba</t>
+    <t>saran ane gan saran ane coba main bazartoto cocok banget kasih modal cadang agan serakah ane jamin agan coba</t>
   </si>
   <si>
     <t>Kita pernah seirama, kini hanya gema</t>
@@ -2611,7 +2805,7 @@
     <t>Cuma di SINDEN4D depo minimal WD MAKSIMAL</t>
   </si>
   <si>
-    <t>sindend minimal deposit maksimum wd</t>
+    <t>sindend minimal deposit maksimal wd</t>
   </si>
   <si>
     <t>Jangan hanya nonton, yuk ikutan</t>
@@ -2624,7 +2818,7 @@
 Serasa PRo kali yakan main nyaa...</t>
   </si>
   <si>
-    <t>pro putar pro putar</t>
+    <t>orang profesional main orang profesional main</t>
   </si>
   <si>
     <t>yuk gaes</t>
@@ -2639,10 +2833,58 @@
     <t>bajing</t>
   </si>
   <si>
+    <t>Deposit 1jt abis ama game kontol ini</t>
+  </si>
+  <si>
+    <t>deposit juta selesai main kontol</t>
+  </si>
+  <si>
+    <t>Cari tau admin aplikasi ini,,bantai mereka</t>
+  </si>
+  <si>
+    <t>cari admin aplikasi bantai</t>
+  </si>
+  <si>
+    <t>member tai 10 x deposit gak pernah ngasih gim miskin</t>
+  </si>
+  <si>
+    <t>anggota tai x deposit main buruk</t>
+  </si>
+  <si>
     <t>apk bangsat kontol babi</t>
   </si>
   <si>
     <t>apk bajing kontol babi</t>
+  </si>
+  <si>
+    <t>Ni admin bangsat juga promoin apk taaaii dancok</t>
+  </si>
+  <si>
+    <t>no admin jalang promosi apk tai dancok</t>
+  </si>
+  <si>
+    <t>Situs tai palat</t>
+  </si>
+  <si>
+    <t>situs tai palat</t>
+  </si>
+  <si>
+    <t>Penipu sialan admin situs ini,,tidak bakalan dibayar kalian</t>
+  </si>
+  <si>
+    <t>tipu sial admin situs bayar</t>
+  </si>
+  <si>
+    <t>ST789 MAINKAN ORG RUMAH KAU AKU MAU BOS KRN PEPEK NYA TEBAL X.</t>
+  </si>
+  <si>
+    <t>st main rumah orang bos kecup tebal x</t>
+  </si>
+  <si>
+    <t>BOS PEPEK MAMA KAU DIKENTOT ANJING BOS</t>
+  </si>
+  <si>
+    <t>bos pepek mama anjing bos tidur</t>
   </si>
   <si>
     <t>Modal dikit hasil manis cuyy
@@ -2682,12 +2924,36 @@
     <t>kecewa pnsel lihat teman posting hasil jepee gilir pamer posting hasil makswin hahaha</t>
   </si>
   <si>
+    <t>Emang apk rr999 tai apk udah di seting</t>
+  </si>
+  <si>
+    <t>apk rr apknya setting</t>
+  </si>
+  <si>
+    <t>Jangan mau deposit disini, deposit lancar giliran penarikan gak mau bayar, apk miskin, agen babi.</t>
+  </si>
+  <si>
+    <t>gak deposit deposit lancar tari gak bayar apk jelek agen babi</t>
+  </si>
+  <si>
+    <t>Ia akun babi ni..akun miskin..depo mulu babi..akun tai..akun paling nipu</t>
+  </si>
+  <si>
+    <t>akun babi akun malang deposit akun tai akun curang</t>
+  </si>
+  <si>
     <t>situs kontol udah depo tpi gk masuk2</t>
   </si>
   <si>
     <t>situs kontol deposit masuk</t>
   </si>
   <si>
+    <t>Situs biadab ini jangan kalian main kan lagi ini</t>
+  </si>
+  <si>
+    <t>main main situs biadab ya</t>
+  </si>
+  <si>
     <t>baru kali ini rasain yang nama nya jackpot cok , padahal cuman bet 800 perak bisa dapat hampir 8 juta , emang mantap banget situs nya 𝐒𝐈𝐁𝐀𝐘𝐀𝐑💰💃</t>
   </si>
   <si>
@@ -2697,7 +2963,7 @@
     <t>Bisa di hp apa aja</t>
   </si>
   <si>
-    <t>ponsel</t>
+    <t>laku ponsel</t>
   </si>
   <si>
     <t>tiap putaran makin nagih! Duit ngalir terus! memang best x dah ⚡𝗣𝗲𝘁𝗮𝗿𝘂𝗻𝗴𝟭𝟯𝟴⚡</t>
@@ -2745,7 +3011,7 @@
     <t>LINK MAIN DI CAPTION ATAS YA 😎</t>
   </si>
   <si>
-    <t>link utama caption oke wajah kacamata hitam</t>
+    <t>link utama caption ya</t>
   </si>
   <si>
     <t>Ayo, waktunya untuk memulai sesuatu yang baru!
@@ -2758,13 +3024,19 @@
     <t>Situs Resmi Internasional</t>
   </si>
   <si>
-    <t>situs internasional resmi</t>
+    <t>situs resmi internasional</t>
+  </si>
+  <si>
+    <t>menyalaa syekali ni mayongggg..</t>
+  </si>
+  <si>
+    <t>mayong terang benderang</t>
   </si>
   <si>
     <t>Guys hoki kalau main 𝐒𝐈𝐁𝐀𝐘𝐀𝐑 langsung jp, kakak yang mau cuan bisa buktiin juga web jagonya jepe.</t>
   </si>
   <si>
-    <t>guys main sibayar untung main langsung gan uang bukti websitenya bagus</t>
+    <t>guys kalo main ente untung kalo main sibayar langsung jp agan agan uang bukti websitenya bagus jepe</t>
   </si>
   <si>
     <t>Ini baru bos.depo20k.dikasih segini</t>
@@ -2773,20 +3045,32 @@
     <t>boss depok</t>
   </si>
   <si>
+    <t>Awas apk penipu jangan instal apalgi main di apk ini ntardi bangsat   ini kumpulan para bangsat berkedok apk bodong</t>
+  </si>
+  <si>
+    <t>hati hati apk palsu install main apk bajing kelompok bajing kedok apk palsu</t>
+  </si>
+  <si>
     <t>Mhmd Kiboll</t>
   </si>
   <si>
-    <t>mhmd kiboll</t>
+    <t>mhmd omong kosong</t>
   </si>
   <si>
     <t>new member 100% TO X3
 hanyan ada di kejarjitu.com yang berani kasih TO rendah BROK.</t>
   </si>
   <si>
-    <t>anggota to x kejarjitu com berani to low broke</t>
+    <t>anggota x kejarjitu com berani harga rendah gan</t>
   </si>
   <si>
     <t>APK ANJING</t>
+  </si>
+  <si>
+    <t>3x depo scatter zonk depo 50 jd 68 terakhir bayangkan sekali gak dapet scatter hebat kan ni situs taik anjing... Warning</t>
+  </si>
+  <si>
+    <t>x deposit scatter zonk deposit kali bayang scatter situs dog taik</t>
   </si>
   <si>
     <t>APK GACOR
@@ -2794,7 +3078,7 @@
 SEGERA DOWNLOAD</t>
   </si>
   <si>
-    <t>apk gacor {LINK} unduh</t>
+    <t>gacor apk {LINK} unduh</t>
   </si>
   <si>
     <t>Baru juga main udah menang,ggak nyesel join yuk ⚡𝗣𝗲𝘁𝗮𝗿𝘂𝗻𝗴𝟭𝟯𝟴⚡</t>
@@ -2818,6 +3102,24 @@
     <t>periksa profil apk hijau ayo download gan wajah senyum mata bahagia</t>
   </si>
   <si>
+    <t>Kalo apk rr4.mi yg kaya gimana kk</t>
+  </si>
+  <si>
+    <t>apk rr mi kaya</t>
+  </si>
+  <si>
+    <t>Hsbi Remitas apk miskin lu promosiin</t>
+  </si>
+  <si>
+    <t>hasbi remitas apk promosi lu buruk</t>
+  </si>
+  <si>
+    <t>Yayak II android</t>
+  </si>
+  <si>
+    <t>yayak ii android</t>
+  </si>
+  <si>
     <t>Terima kasih 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢 sdh kasi gw Maxxwiin di majong, emang nasib rezeki anak baik 😇😇, 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢 🚀🚀🚀🚀🚀🚀</t>
   </si>
   <si>
@@ -2827,25 +3129,25 @@
     <t>Gue member baru main sehari aja udah JiPi 3 kali! Keren abis sih 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢, JARANG ADA tempat main kaya 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢 !!!!</t>
   </si>
   <si>
-    <t>anggota main jip kali keren banget bazartoto jarang main bazartoto</t>
+    <t>anggota main laku jip kali keren banget bazartoto jarang temu main bazartoto</t>
   </si>
   <si>
     <t>Sebenarnya aku ga mau ikutan komen beginian, tapi cemana lah aku uda 5 hari beruntun cair trs dari 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢, kemarin depoh sekali doang ku sisain dikit buat main tiap hari tapi malah cair trs hehehee</t>
   </si>
   <si>
-    <t>komentar daya cair bazartoto kemarin uang sisa main cair hehehee</t>
+    <t>komentar daya cair bazartoto kemarin uang sisa main habis hehehee</t>
   </si>
   <si>
     <t>Tadi malam aku sebelum tdr coba nyepiin di 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢, modaal 80rb weedeh ku tembus sampai 3jt an, anjir sampai ga bisa tidur semalaman tp worth it bangett ahahahaha😂😂</t>
   </si>
   <si>
-    <t>malam tidur coba masuk bazartoto modal ribu weedeh capai juta tidur malam worth it banget ahahahaha wajah gembira urai air mata wajah gembira urai air mata</t>
+    <t>malam tidur coba masuk bazartoto modal ribu weedeh juta malam tidur worth it banget ahahahaha wajah gembira urai air mata wajah gembira urai air mata</t>
   </si>
   <si>
     <t>🔥𝐆𝐌𝐓𝐒𝐋𝐎𝐓🔥 muantap banget nih rekomennya pasti Wede</t>
   </si>
   <si>
-    <t>api gmtslot api bagus rekomendasi wede</t>
+    <t>api gmtslot api mantap banget pokok recomended</t>
   </si>
   <si>
     <t>Takdir memisah, hati menolak menyerah</t>
@@ -2863,20 +3165,39 @@
     <t>Gw dengar2 bukan hanya gw yg jipi di 𝐁𝐀𝐙𝐀𝐑𝐓𝐎𝐓𝐎 belakangan ini, gila sih gw sama kawan kawan pada weedeh disana 😍😍</t>
   </si>
   <si>
-    <t>dengar bahaya weedeh gila gila teman teman weedeh wajah senyum lebar mata hati wajah senyum lebar mata hati</t>
+    <t>dengar nge jeping bazartoto gila teman teman weedeh wajah senyum lebar mata hati wajah senyum lebar mata hati</t>
   </si>
   <si>
     <t>Nge-spin di 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢 rasanya kayak dapet angin segar, hoki terus tiap hari 🤑🤑🤑🤑🤑🤑,  LADANG DUIT GUA INI 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢 !!!!</t>
   </si>
   <si>
-    <t>putar bazartoto serasa hirup udara segar moga sukses wajah materialistis wajah materialistis wajah materialistis wajah materialistis wajah materialistis wajah materialistis lapang uang gua bazartoto</t>
+    <t>putar bazartoto serasa hirup udara segar moga sukses wajah materialistis wajah materialistis wajah materialistis wajah materialistis wajah materialistis wajah materialistis ladang uang bazartoto</t>
+  </si>
+  <si>
+    <t>ramai kan ,lagi gacor nih</t>
+  </si>
+  <si>
+    <t>sibuk gila</t>
+  </si>
+  <si>
+    <t>𝑺𝒖𝒑𝒆𝒓 𝒃𝒂𝒊𝒌💯🌊</t>
+  </si>
+  <si>
+    <t>super nilai ratus ombak</t>
   </si>
   <si>
     <t>Udah banyak yang buktiin, sekarang giliran kamu!
 Gaskeun sekarang juga, biar cuan makin deras! ketik aja di google 𝗕𝗔𝗬𝗔𝗠𝟭𝟮𝟯</t>
   </si>
   <si>
-    <t>bukti gilir gaskeun uang alir ketik google bayam</t>
+    <t>bukti gilir gaskeun biar uang ketik google bayam</t>
+  </si>
+  <si>
+    <t>𝑺𝒖𝒑𝒆𝒓 𝒃𝒂𝒊𝒌💯🌊
+𝑺𝒖𝒑𝒆𝒓 𝒃𝒂𝒊𝒌💯🌊</t>
+  </si>
+  <si>
+    <t>super nilai ratus ombak super nilai ratus ombak</t>
   </si>
   <si>
     <t>aku juga barusan dikaslh 7jt di 𝐁𝐀𝐘𝐀𝐌𝟏𝟐𝟑..lamaa gak maen bisa jepe juga dsni , mantap emg terima kasihhh yah 𝐁𝐀𝐘𝐀𝐌𝟏𝟐𝟑, joss terkenal ni web mantapp ada jual beli JUGA ...</t>
@@ -2906,13 +3227,28 @@
     <t>Ini bos.yakin lah ..</t>
   </si>
   <si>
-    <t>bos</t>
+    <t>Hari ini saya WD.ini Poto nya..</t>
+  </si>
+  <si>
+    <t>pergi foto</t>
+  </si>
+  <si>
+    <t>Untuk WD saya hari ini..</t>
+  </si>
+  <si>
+    <t>wdku</t>
+  </si>
+  <si>
+    <t>Modal 20k....</t>
+  </si>
+  <si>
+    <t>modal k</t>
   </si>
   <si>
     <t>Beneran di kasih naga itam main di 𝐁𝐀𝐙𝐀𝐑𝐓𝐎𝐓𝐎, modal goban cair 3jt gookill abiss wkwkwk, mahyong prakmatik emaang lagii maantap di 𝐁𝐀𝐙𝐀𝐑𝐓𝐎𝐓𝐎 🤣🤣</t>
   </si>
   <si>
-    <t>beneran kasih naga hitam main bazartoto modal gob cair juta gookillnya hilang hahaha mahjong praktis mantap banget bazartoto tertawa bahak bahak tertawa bahak bahak</t>
+    <t>bener kasih naga hitam main bazartoto gob cair modal juta gookill habis hahaha mahjong praktis mantap banget bazartoto tertawa bahak bahak tertawa bahak bahak</t>
   </si>
   <si>
     <t>Kunci dari semua masalah ini</t>
@@ -2930,19 +3266,19 @@
     <t>bagi kalian yg belom tau 🌟𝗦𝗜𝗗𝗢𝟴𝟴🌟 coba maen disana supaya tau web asli yg profesional fair itu gmn.🌟𝗦𝗜𝗗𝗢𝟴𝟴🌟 situs  Terpercaya jd menurut gw paling aman kalo maen di web besar. Coba aja sendiri bang .</t>
   </si>
   <si>
-    <t>coba main website asli adil profesional coba kawan</t>
+    <t>coba main website asli adil profesional coba gan</t>
   </si>
   <si>
     <t>Hidup lagi cape-capenya malah dikasih kejutan sama 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢, uang makan sama bensin bulan ini aman terkendali wkwkwk</t>
   </si>
   <si>
-    <t>hidup capek banget kasih kejut bazartoto uang makan bensin aman kendali hahaha</t>
+    <t>capek hidup sampe kasih kejut bazartoto uang makan bensin aman kendali hahaha</t>
   </si>
   <si>
     <t>seperti 🌟𝗦𝗜𝗗𝗢𝟴𝟴🌟 Lebih baik sederhana tapi sangat setia daripada banyak gaya tapi bikin hati terluka</t>
   </si>
   <si>
-    <t>like bintang sinar sido bintang sinar sederhana setia gaya hati luka</t>
+    <t>suka bintang sinar sido bintang sinar sederhana setia banget gaya bikin hati sakit</t>
   </si>
   <si>
     <t>yang paling bener emang 𝗣𝗢𝗡𝗦𝗘𝗟𝟲𝟵 , tiap kali main game apapun rata rata pecahannya lebih bagus dan bs menang gampang pecah nya .. aku sih iseng awalnya tapi sekarank setia di situs 𝗣𝗢𝗡𝗦𝗘𝗟𝟲𝟵</t>
@@ -2960,7 +3296,13 @@
     <t>Sahabat bukan yang datang hanya saat butuh, tapi tetap ada saat kamu butuh</t>
   </si>
   <si>
-    <t>sahabat butuh butuh</t>
+    <t>sahabat orang butuh butuh</t>
+  </si>
+  <si>
+    <t>Situs paling buruk pelit nya PARAH FUCK</t>
+  </si>
+  <si>
+    <t>situs jelek pelit jelek banget</t>
   </si>
   <si>
     <t>24/06/2025
@@ -2971,7 +3313,19 @@
 👉👉 LINK CEK DI BIO KU SALAM JP</t>
   </si>
   <si>
-    <t>bonus anggota dp lode anggota manja arah kanan arah kanan lihat link bio salam jp</t>
+    <t>bonus anggota dp lode anggota manja arah kanan arah kanan cek link bio salam jp</t>
+  </si>
+  <si>
+    <t>Situs tai gk bisa tarik saldo</t>
+  </si>
+  <si>
+    <t>situs tai tarik saldo</t>
+  </si>
+  <si>
+    <t>Apk anjing gak usa sok sok dasar semoga yang buat apk ini ya mati 7 turunan tanpa terkecuali dari admin admin nya Ampe bos" nya semoga kebohongan kalian itu di gantikan dengan meninggal nya keluarga kalian 1 per 1 amin ya rabbal allamin</t>
+  </si>
+  <si>
+    <t>apk anjing gak work sok basic moga apk mati generasi kecuali admin admin bos moga bohong ganti mati keluarga aamiin ya rabbal allamine</t>
   </si>
   <si>
     <t>lagi   langsung  aja   bos Member
@@ -2980,13 +3334,25 @@
 https://heylink.me/KakekVIPP/</t>
   </si>
   <si>
-    <t>langsung ya bos member kasih maxwin rutin kali x pecah bagus banget asli herod cantik gacor kalo maxwin langsung wd pola setting langsung link parah daftar pake akun sukses on bos bank cek rtpnya {LINK}</t>
+    <t>langsung bos member kasih maxwin rutin turun kali x pecah bagus banget original herod bagus banget keren banget maxwin langsung aja pola settingnya link parah daftar pakai akun sukses aktif bos bank cek rtp {LINK}</t>
+  </si>
+  <si>
+    <t>Apk anjing babi Rungkat terus setan lu</t>
+  </si>
+  <si>
+    <t>apk rungkat babi anjing setan</t>
   </si>
   <si>
     <t>Bergabunglah dengan Jktjkt dan dapatkan bonus luar biasa! https://jktlionspin.vip/?c=DR4TZP</t>
   </si>
   <si>
     <t>gabung jktjkt bonus {LINK}</t>
+  </si>
+  <si>
+    <t>Apk sedot WC setan lu goblok Apk babi anjing   id:419981087</t>
+  </si>
+  <si>
+    <t>apk toilet sedot setan bodoh apk anjing babi id</t>
   </si>
   <si>
     <t>28.06
@@ -3040,7 +3406,7 @@
 ‎?pid=518329063&amp;pkg=com.luck.bet</t>
   </si>
   <si>
-    <t>aplikasi gas botakin wajah materialistis {LINK} putar wajah materialistis {LINK} permata wajah materialistis {LINK} remi wajah materialistis {LINK} id {LINK} moga untung wajah materialistis {LINK} untung wajah materialistis sharelucksvip top pid pkg com lucksvip app wajah materialistis {LINK} wajah materialistis shareluck asia pid pkg com luck bet</t>
+    <t>apk gas balakin wajah materialistis {LINK} putar wajah materialistis {LINK} permata wajah materialistis {LINK} remi wajah materialistis {LINK} id {LINK} untung wajah materialistis {LINK} untung wajah materialistis sharelucksvip top pid pkg com lucksvip app wajah materialistis {LINK} wajah materialistis shareluck asia pid pkg com luck bet</t>
   </si>
   <si>
     <t>Apk gacor
@@ -3048,20 +3414,17 @@
 Dowload sekarang</t>
   </si>
   <si>
-    <t>gacor apk {LINK} unduh</t>
-  </si>
-  <si>
     <t>!! DEPOSIT RP 10RIBU DAPAT BONUS 25RIBU!! 
   (EVENT TERBARU HANYA SAMPAI TGL 12 MEI) https://www.tt343.com?chn=bnRfeW43NzdfY3Qz&amp;id=MjU5NjM5NDA2</t>
   </si>
   <si>
-    <t>deposit rp bonus acara mei {LINK}</t>
+    <t>deposit rp ribu bonus ribu acara mei {LINK}</t>
   </si>
   <si>
     <t>Cuma 𝐁𝐎𝐍𝐆𝐄𝐒𝐋𝐎𝐓 yang bikin aku nyaman bermain, soalnya WD berapapun pasti di bayar.</t>
   </si>
   <si>
-    <t>bongeslot nyaman main wd jamin bayar</t>
+    <t>bongeslot nyaman main uang bayar bayar</t>
   </si>
   <si>
     <t>Ayo mulai perjalanan baru ini bersama-sama
@@ -3086,448 +3449,13 @@
     <t>Main sI0000t di 𝐁𝐀𝐘𝐀𝐌𝟏𝟐𝟑 tuh bener-bener bikin nagih bang !! Cuma pencet2 bentar aja uda jp , 𝐁𝐀𝐘𝐀𝐌𝟏𝟐𝟑 emang the best.....</t>
   </si>
   <si>
-    <t>main sit bayam bikin tagih tekan sebentar selesai bayam</t>
+    <t>main sit bayam bikin tagih tekan sebentar selesai bayam mantap pokok</t>
   </si>
   <si>
     <t>bulan juni ini gw hoki banget main di 𝐒𝐆𝐀𝟑𝟑𝟖 dor doran menang jackpotnya mantap kali la^^</t>
   </si>
   <si>
     <t>juni untung banget main sga dor dor jackpot mantap la</t>
-  </si>
-  <si>
-    <t>Memang gila bener main di 𝐁𝐀𝐘𝐀𝐌𝟏𝟐𝟑 baru pertama kali main langsung di kasih WEDE JUTAAN🥰🥰</t>
-  </si>
-  <si>
-    <t>gila banget main bayam kali main langsung kasih wede juta wajah senyum hati wajah senyum hati</t>
-  </si>
-  <si>
-    <t>aku jamin kalau main di 🥳 🔥S O P I 8 8🔥 🥳 menang berapa aja pasti lunassss, 🥳 🔥 S O P I 8 8 🔥🥳 sangat terpercaya pokonya pollll !a</t>
-  </si>
-  <si>
-    <t>jamin main wajah pesta api s o p i api wajah pesta menang bayar wajah pesta api s o p i api wajah pesta handal banget pol</t>
-  </si>
-  <si>
-    <t>Kalau gw sih betahh main di 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢, proomosi mereka paliing lengkapp siitusnya jg gampang diakses enak lah pokonya main disana gw acungin jempool 👍👍👍</t>
-  </si>
-  <si>
-    <t>betah banget main bazartoto promosi lengkap situs mudah akses enak banget main acung jempol jempol jempol jempol</t>
-  </si>
-  <si>
-    <t>Kau menggenggam kumenadahnya</t>
-  </si>
-  <si>
-    <t>pegang tahan</t>
-  </si>
-  <si>
-    <t>Kisah yang tak usai meski telah usai</t>
-  </si>
-  <si>
-    <t>buah cerita</t>
-  </si>
-  <si>
-    <t>Barusan cair 4,2jt dari 𝐁𝐀𝐙𝐀𝐑𝐓𝐎𝐓𝐎,padahal cuma karena iseng ikutin saran teman modal 70rb wkwk mahyong2 nya emgg supeer gokiiill 🤣🤣</t>
-  </si>
-  <si>
-    <t>cair jt bazartoto iseng iseng saran teman modal rb mahjongnya super gokill tertawa bahak bahak tertawa bahak bahak</t>
-  </si>
-  <si>
-    <t>Berdamai dengan apa yang terjadi</t>
-  </si>
-  <si>
-    <t>damai</t>
-  </si>
-  <si>
-    <t>maen online tuh uda pasti di 🌟𝗦𝗜𝗗𝗢𝟴𝟴🌟 aja bosku. kalo mau maen cari web yg jelas dan aman . biar bergaransi kalau menang pasti cair itu aja sih intinya menurut gw</t>
-  </si>
-  <si>
-    <t>main online tugas bos main cari website aman jamin menang inti</t>
-  </si>
-  <si>
-    <t>Bisa main kapan aja, di mana aja 𝐒𝐔𝐏𝐄𝐑𝐂𝐔𝐀𝐍𝟖𝟖🍻Banyak game lain juga di situ 𝐒𝐔𝐏𝐄𝐑𝐂𝐔𝐀𝐍𝟖𝟖🍺</t>
-  </si>
-  <si>
-    <t>main supercuan mug bir denting main supercuan mug bir</t>
-  </si>
-  <si>
-    <t>Aku kemarin di rekomen teman main di 𝐁𝐀𝐙𝐀𝐑𝐓𝐎𝐓𝐎, awalnya sihh saldo ku turun uda hampir habis langsung dikagetin sketer perkalian gedeekk wkwkwk, pertama kali ngerasaain mekswin makasih banyak 𝐁𝐀𝐙𝐀𝐑𝐓𝐎𝐓𝐎 😘😘</t>
-  </si>
-  <si>
-    <t>kemarin rekomendasi teman main bazartoto saldo turun habis langsung kaget kali hahahaha kali mekswin terima kasih bazartoto wajah cium wajah cium</t>
-  </si>
-  <si>
-    <t>Top-up langsung dapat koin bonus! Teman Top-up 2.000.000, langsung dapat 20.000 koin! Menang terus, seru tiada henti — mainkan D73 sekarang! https://d73realm.lol/?channelCode=M1029077</t>
-  </si>
-  <si>
-    <t>top up langsung koin bonus teman top up koin menang senang main d {LINK}</t>
-  </si>
-  <si>
-    <t>Padahal cuma maen santai di 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢, eh tiba-tiba saldo gue nambah aja 😂😂😂😂😂 , 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢 JOSS ABIEZZZZ !!</t>
-  </si>
-  <si>
-    <t>main santai bazartoto saldo wajah gembira urai air mata wajah gembira urai air mata wajah gembira urai air mata wajah gembira urai air mata wajah gembira urai air mata bazartoto joss abiez</t>
-  </si>
-  <si>
-    <t>Malas mau jelasin ke orang2 yang ga mau percaya, yang jelas selama ini aku selalu dikasih menaang sama 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢, siitus paling dermawan selama aku main hahahaha</t>
-  </si>
-  <si>
-    <t>malas orang percaya menang bazartoto situs dermawan main hahahaha</t>
-  </si>
-  <si>
-    <t>Belakangan ga di facebook ga di instagram orang2 pada komen 𝐁𝐀𝐙𝐀𝐑𝐓𝐎𝐓𝐎 , sekali tak coba ternyata beneran kasih, mayan lahh walaupun bukan mekswin tapi cukup lah buat bayar cicilan hehehe</t>
-  </si>
-  <si>
-    <t>facebook instagram komen bazartoto coba nyata suka banget mantap mekswin bayar cicil hehehe</t>
-  </si>
-  <si>
-    <t>Terserah lu mau percaya atau ga bang, tapi yang jelas lu ga bakal nyesal lah main di 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢, aku sama kawan2 setongkrongan pada nyarii cuaan disini, gokil parah 👍👍</t>
-  </si>
-  <si>
-    <t>serah percaya sesal main bazartoto teman teman cari untung gila banget jempol jempol</t>
-  </si>
-  <si>
-    <t>Bocoran dari forum sebelah Jam gacornya 🌟𝗦𝗜𝗗𝗢𝟴𝟴🌟 di [siang jam 12:32 - 12:56] [sore Jam 15:02 - 16:17] [Malam jam 19:42 - 20:12] di catet GUYS!!</t>
-  </si>
-  <si>
-    <t>bocor forum belah jam gacor bintang sinar sido bintang sinar jam siang sore sore catat guys</t>
-  </si>
-  <si>
-    <t>Kau pernah menjadi rumah, kini hanya kenangan</t>
-  </si>
-  <si>
-    <t>rumah tinggal kenang</t>
-  </si>
-  <si>
-    <t>Fatchur Rochman gas</t>
-  </si>
-  <si>
-    <t>gas fathur rochman</t>
-  </si>
-  <si>
-    <t>Nisa Dila oke siap</t>
-  </si>
-  <si>
-    <t>nisa dila oke</t>
-  </si>
-  <si>
-    <t>Ada begitu banyak cara agar kamu bisa maju, akan tetapi hanya ada satu cara untuk tetap diam. 🛜</t>
-  </si>
-  <si>
-    <t>gerak maju diam nirkabel</t>
-  </si>
-  <si>
-    <t>Makasih *@MAHASLOT* Sekian lama main, baru kali ini gw bener2 ngerasain yang namanya Maxxwin</t>
-  </si>
-  <si>
-    <t>thanks mahaslot udah main kali ngerasain nama maxxwin</t>
-  </si>
-  <si>
-    <t>Memang gila bener main di 𝐁𝐎𝐍𝐆𝐄𝐒𝐋𝐎𝐓 baru pertama kali main langsung di kasih WEDE JUTAAN🥰🥰</t>
-  </si>
-  <si>
-    <t>gila banget main bongeslot kali main langsung kasih wede juta wajah senyum hati wajah senyum hati</t>
-  </si>
-  <si>
-    <t>Ayo mulai perjalanan baru ini bersama-sama</t>
-  </si>
-  <si>
-    <t>mari jalan</t>
-  </si>
-  <si>
-    <t>Lagi enak kak
-https://www.6svipa.com?chn=NnN2aXBfaWQzX250bGE0&amp;id=MjcxNzIxMjA4</t>
-  </si>
-  <si>
-    <t>enak kak {LINK}</t>
-  </si>
-  <si>
-    <t>Hari ini milik gue! Jackpot masuk tanpa ampun! ⚡𝗣𝗲𝘁𝗮𝗿𝘂𝗻𝗴𝟭𝟯𝟴⚡</t>
-  </si>
-  <si>
-    <t>milik jackpot ampun tegang tarung tegang</t>
-  </si>
-  <si>
-    <t>Deposit 50k dapat bonus 20k bosku.. di aplikasi 📥
-https://share567luck.org?pid=439054694&amp;pkg=com.luck.bet</t>
-  </si>
-  <si>
-    <t>deposit rb bonus rb bos aplikasi baki kotak masuk {LINK}</t>
-  </si>
-  <si>
-    <t>apk baru gacor parah🔥
-https://sharemainduit.click?pid=294304754&amp;t=pdd2&amp;pkg=com.mainduit08.app</t>
-  </si>
-  <si>
-    <t>apk serius api {LINK}</t>
-  </si>
-  <si>
-    <t>💥Aku sudah memenangkan Rp8000000! 💰 Klik tautan bermain gratis dan mulailah menghasilkan!   https://moneyeveryday-iqqqud.top?pid=r_917513667535052</t>
-  </si>
-  <si>
-    <t>tabrak menang rp kantung uang klik taut putar gratis hasil uang {LINK}</t>
-  </si>
-  <si>
-    <t>Ow gila tak masuk logika</t>
-  </si>
-  <si>
-    <t>barusan gw maen olympus 1000 kmren turun pecah x1000 di  habis tu main di 𝗣𝗢𝗡𝗦𝗘𝗟𝟲𝟵  padahal gk scatter dapat maxwin 15juta hhehe ..thanks 𝗣𝗢𝗡𝗦𝗘𝗟𝟲𝟵 , temen ku juga dpat bisa lagi viral rokok gara gara cobain situs ini</t>
-  </si>
-  <si>
-    <t>main olympus kmren tembus x main ponsel gak hambur maxwin juta hhehe makasih ponsel sobat rokok viral coba situs</t>
-  </si>
-  <si>
-    <t>Aku sambil rebahan jg dapat uang jajan dari 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢, modarl 50rb doang main ga sampe 15 menit cair 900rb wkwkwk lumayan lah buat isi bensin sama rokok hehehe</t>
-  </si>
-  <si>
-    <t>rebah uang jajan bazartoto modal rb main menit bayar rb hahaha lumayan isi bensin rokok hehehe</t>
-  </si>
-  <si>
-    <t>Main di BO mana pun selalu ada kecewanya.. Gw pernah kecewa 2x main 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢, tp di senangin 7x ama kejutannya 🥰🥰🥰🥰🥰𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢 GACHOOORRRR 🥰🥰🥰🥰🥰</t>
-  </si>
-  <si>
-    <t>main bo kecewa udah kali kecewa main bazartoto x senang kejut wajah senyum hati wajah senyum hati wajah senyum hati wajah senyum hati wajah senyum hati bazartoto gachor wajah senyum hati wajah senyum hati wajah senyum hati wajah senyum hati wajah senyum hati</t>
-  </si>
-  <si>
-    <t>Jangan sampai salah pilih seperti situs yang lain nya, 💥 kalau mau cari yang pasti ya 🔥🔥𝐆 𝐄 𝐑 𝐀 𝐈 𝐓 𝟎 𝐆 𝐄 𝐋🔥🔥 aja sudah pasti terbaik Bayarrr......</t>
-  </si>
-  <si>
-    <t>salah pilih situs tabrak cari api api g e r a i t g e l api api bayar</t>
-  </si>
-  <si>
-    <t>Ini soal hati bukan yang diyakini</t>
-  </si>
-  <si>
-    <t>hati orang</t>
-  </si>
-  <si>
-    <t>Kemarin aku pecah rekor bang, main di 𝐁𝐀𝐙𝐀𝐑𝐓𝐎𝐓𝐎 modal 100reboo doang wedeh ku tembus 6jt-an aku main mahyông2 sama wild banditôô gokilll wkwkkwk🤣🤣</t>
-  </si>
-  <si>
-    <t>kemarin pecah rekor gan main bazartoto modal reboo juta main mahyong bandit liaroo gokil hahaha tertawa bahak bahak tertawa bahak bahak</t>
-  </si>
-  <si>
-    <t>Fatchur Rochman LINK MAIN DI CAPTION ATAS YA 😎</t>
-  </si>
-  <si>
-    <t>link utama fatchur rochman caption wajah kacamata hitam</t>
-  </si>
-  <si>
-    <t>🎮 Ayo main bareng RAJASEMAR! Temukan keseruan game seru dan raih bonus menarik setiap harinya! Siap menang dengan cara seru? 💥</t>
-  </si>
-  <si>
-    <t>video game ayo main rajasemar temu seru main seru menang bonus tarik menang senang tabrak</t>
-  </si>
-  <si>
-    <t>'Baru main sebentar, 🚀🚀udah dikasih petir berkali-kali! ⚡💥Kalo udah di ⭐️SOPI88 ⭐️💣💣, siap-siap dompet makin tebal! 👍Gas terus sampe senyum gak berhenti! 😎💸🔥''</t>
-  </si>
-  <si>
-    <t>main sebentar roket roket kena petir kali kali tegang tabrak bintang medium putih sopi bintang medium putih bom bom dompet tebal jempol gas senyum henti wajah kacamata hitam uang sayap api</t>
-  </si>
-  <si>
-    <t>Jangan sampai salah pilih seperti situs yang lain nya, 💥 kalau mau cari yang pasti ya 🔥🔥#MAHASLOT🔥🔥 aja sudah pasti dibayar lunas</t>
-  </si>
-  <si>
-    <t>salah pilih situs tabrak cari tinggal api api mahaslot api api bayar full</t>
-  </si>
-  <si>
-    <t>@semua orang</t>
-  </si>
-  <si>
-    <t>orang</t>
-  </si>
-  <si>
-    <t>Situs tergacor deposit cuma 10k bisa Withdraw, Withdraw bisa 10k, download melalui link yang saya bagikan agar akun nya sama-sama gacor.
-https://www.tt343.com?chn=eW43NzdfaWQ2X250bGEx&amp;id=NjkyNTM2MTQy</t>
-  </si>
-  <si>
-    <t>situs tergacor deposit rb withdraw withdraw rb download link share biar akun gacor {LINK}</t>
-  </si>
-  <si>
-    <t>2️⃣9️⃣
-Bonus new member 100% cuman di #lode777 tempat bermain paling mantap
-DP 30+30
-DP 50+50
-100+100
-✴️Link daftar ada di bio</t>
-  </si>
-  <si>
-    <t>keycap keycap bonus member lode main dp dp bintang ujung delapan link daftar bio</t>
-  </si>
-  <si>
-    <t>APK SL0T GACOR
-APK HIJAU
-winidn:
-https://www.winidnbet6.com?code=669Y82JKCHK&amp;t=1750830756
-898a: 
-898a3.com?code=W3ADHN1C6YA&amp;t=1750830831
-gems 365:
-https://www.gems365777.com?code=BRK5R8LERVL&amp;t=1750830920
-spin harta:
-https://www.spinharta48.com?code=M7CJL29FGQ8&amp;t=1750831147
-remi101:
-https://www.remi101vip13.cc?code=VZH7W8T6NS8&amp;t=1750831279
-jaya slot:
-https://www.jayaslot79.com?code=2C0XSKKFYF5&amp;t=1750831358
-APK OREN
-88id: baru
-https://share88id.net?pid=482793838&amp;t=pdd2&amp;pkg=com.new88id.app
-idn 777: baru
-https://idn7777.me?pid=269796801&amp;t=pdd2&amp;pkg=com.idn777.app
-luck svip:
-https://share8.lucksvip7.cyou?pid=500164499&amp;t=pdd2&amp;pkg=com.lucksvip.app
-rp game:
-https://share0.rpgames.me?pid=392428510&amp;t=pdd2&amp;pkg=com.rpgame.app
-dana game:
-https://sharedanagame.cc?pid=460822035&amp;t=pdd2&amp;pkg=com.danagame.app
-789rp:
-https://share3.789rp.org?pid=377062826&amp;t=pdd2&amp;pkg=com.rp789.game
-567luck: baruu
-https://share567luck.shop?pid=352712395&amp;t=pdd2&amp;pkg=com.luck.bet
-main duit: baru
-https://sharemainduit.autos?pid=417016990&amp;t=pdd2&amp;pkg=com.mainduit17.app</t>
-  </si>
-  <si>
-    <t>apk slt gacor apk hijau menang {LINK} a a com code wadhncya t permata {LINK} putar harta karun {LINK} remi {LINK} slot jaya {LINK} oren apk id {LINK} id {LINK} moga untung svip {LINK} main rp {LINK} dana main {LINK} rp {LINK} untung {LINK} main uang {LINK}</t>
-  </si>
-  <si>
-    <t>Bagikan tautan rujukan ke teman Anda untuk mulai mendapat penghasilan  https://18kekayaan.jaringankeamananvip.com?code=D3YJEJJ596U&amp;t=1750864588</t>
-  </si>
-  <si>
-    <t>link referral teman hasil {LINK}</t>
-  </si>
-  <si>
-    <t>siang tadi gue spin slot Koi Gate di 𝐒𝐔𝐏𝐄𝐑𝐂𝐔𝐀𝐍𝟖𝟖, hasilnya big win!!</t>
-  </si>
-  <si>
-    <t>siang putar slot koi gate supercuan hasil menang</t>
-  </si>
-  <si>
-    <t>2️⃣5️⃣
-Sekarang kamu gak usah bingung lagi karna ada 𝐌𝐀𝐂𝐀𝐍𝐓𝟎𝐆𝐄𝐋 yang selalu kasih kejutan besar dan bonus melimpaahh!
-Semakin Besar Bonusnya,, Semakin Besar Kemenangan nya
-Welcome Bonus 100% (Member baru)
-DP 50 + 50
-DP 100 + 100
-Gasspoll klaim gak pake ribet bonus langsung didepan.
-Linknyaa : dub.sh/promohoki</t>
-  </si>
-  <si>
-    <t>keycap keycap bingung macantgel kejut bonus limpah bonus menang bonus selamat anggota dp dp gasspoll klaim langsung bonus rumit taut dub sh promohoki</t>
-  </si>
-  <si>
-    <t>https://zn4r8tfd.com?chn=c2t5OTlfaWQ0X250bGExNzI=&amp;id=NjczNDUxMTE5
-Yang tau ajaaa</t>
-  </si>
-  <si>
-    <t>{LINK}</t>
-  </si>
-  <si>
-    <t>https://www.rrvip8.com?chn=bnRfcnI3NzdfY3Qy&amp;id=MzQ1NjYxMjg0
-Mantul gays</t>
-  </si>
-  <si>
-    <t>{LINK} teman teman</t>
-  </si>
-  <si>
-    <t>2 APK BARU RILIS YAKIN GACOR
-88id
-https://share88id.vip?pid=391510418&amp;pkg=com.new88id.app
-IDN7777
-https://idn7777.cfd?pid=356198171&amp;pkg=com.idn777.app
-kalo gabisa masuk link pake vvn 1.1</t>
-  </si>
-  <si>
-    <t>apk rilis gacor id {LINK} idn {LINK} masuk taut vvn</t>
-  </si>
-  <si>
-    <t>apk  mantapp 🥰🥰🥰
-https://www.sp252.com?chn=c3BpbnJwX2lkX250bGEyMTM=&amp;id=ODE5NDA2OTU2
-https://cvvip8.com?chn=Y3Y3NzdfaWQ1X250bGE3OQ==&amp;id=OTI5MjAwMDM5
-https://www.sky9905.com?chn=bnRfc2t5OTlfY3Qz&amp;id=MTcyMjE1NTY2
-https://www.v98.online?chn=djk4X2lkNl9udGxhMjM=&amp;id=NTExNDA5MDUx
-https://www.rrvip8.com?chn=cnI3NzdfaWQ3X250bGE0NA==&amp;id=OTMyNjMxMzk4</t>
-  </si>
-  <si>
-    <t>apk bagus wajah senyum hati wajah senyum hati wajah senyum hati {LINK} {LINK} {LINK} {LINK} {LINK}</t>
-  </si>
-  <si>
-    <t>Dijamin WD gua abis dikasih 400rb cuman deposit 25k di apk ini linknya
-https://www.e88vip11.com?chn=ZTg4X2lkNF9udGxhMTE=&amp;id=MzE0OTY0MjM4</t>
-  </si>
-  <si>
-    <t>jamin wd kasih k deposit k link apk {LINK}</t>
-  </si>
-  <si>
-    <t>Kuncinya sabar dan pinter liat pola aja bang. Di 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢, gue sering dapet JiPi perkara main santuy ga terburu-buru... 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢 tempat yang tepat sih buat bermain !!</t>
-  </si>
-  <si>
-    <t>kunci sabar cerdas lihat pola gan bazartoto jip main buru buru bazartoto main</t>
-  </si>
-  <si>
-    <t>Sama bang berkat jipi switbonasa di 𝐁𝐀𝐙𝐀𝐑𝐓𝐎𝐓𝐎 tadi malam, gw langsung berhenti kerja bang ini rencana mau jadiin modal buat buka warung, terima kasih banget 𝐁𝐀𝐙𝐀𝐑𝐓𝐎𝐓𝐎 emang terbaik 😘😘😘</t>
-  </si>
-  <si>
-    <t>gan makasih jip switbonasa bazartoto malam langsung kerja gan rencana modal buka toko terima kasih bazartoto sungguh wajah cium wajah cium wajah cium</t>
-  </si>
-  <si>
-    <t>Biar waktu yang menjawab ragu ini</t>
-  </si>
-  <si>
-    <t>biar ragu</t>
-  </si>
-  <si>
-    <t>Gilaa !! Gw barusan jipi besar di 𝗕𝗔𝗭𝗔𝗥𝗧𝗢𝗧𝗢, emang muantapp poll modal penasaraan jadi kemeenangaann gokill 😂😂😂</t>
-  </si>
-  <si>
-    <t>gila barusan jepi gede bazartoto enak banget polling modal penasaran menang gokill wajah gembira urai air mata wajah gembira urai air mata wajah gembira urai air mata</t>
-  </si>
-  <si>
-    <t>Lumayan buat isi waktu luang 𝐒𝐔𝐏𝐄𝐑𝐂𝐔𝐀𝐍𝟖𝟖⚡Sekali coba, langsung ngerti kenapa rame 𝐒𝐔𝐏𝐄𝐑𝐂𝐔𝐀𝐍𝟖𝟖☄️</t>
-  </si>
-  <si>
-    <t>lumayan isi luang supercuan tegang coba langsung paham populer supercuan komet</t>
-  </si>
-  <si>
-    <t>Bukan clickbait, bisa langsung ngerasain 𝐒𝐔𝐏𝐄𝐑𝐂𝐔𝐀𝐍𝟖𝟖🌪️Coba deh, gue iseng aja malah hoki 𝐒𝐔𝐏𝐄𝐑𝐂𝐔𝐀𝐍𝟖𝟖🌈</t>
-  </si>
-  <si>
-    <t>clickbait langsung asa supercuan tornado coba senang senang untung supercuan pelangi</t>
-  </si>
-  <si>
-    <t>🕹️ 𝗕𝘂𝗸𝗮𝗻 𝗸𝗲𝗯𝗲𝘁𝘂𝗹𝗮𝗻 𝗸𝗮𝗹𝗼 𝗺𝗲𝗻𝗮𝗻𝗴 𝘁𝗲𝗿𝘂𝘀 — 𝗜𝗡𝗗𝗢𝗝𝗔𝗬𝗔𝟭𝟲𝟴 𝗌𝗎𝖽𝖺𝗁 teruji</t>
-  </si>
-  <si>
-    <t>joystick kalo menang indojaya uji</t>
-  </si>
-  <si>
-    <t>Apk baru rilis Gacor banget 
-https://www.33zk.com?chn=bnRfMzN6a19jdA==&amp;id=NzY0MDExODE4</t>
-  </si>
-  <si>
-    <t>apk rilis gacor keren banget {LINK}</t>
-  </si>
-  <si>
-    <t>Gacor abis brayy Bergabunglah dengan Jktjkt dan dapatkan bonus luar biasa! https://jktjkt7.com/?c=XHBHS5</t>
-  </si>
-  <si>
-    <t>gacor selesai broyy gabung jktjkt bonus {LINK}</t>
-  </si>
-  <si>
-    <t>♻️ EVENT PARLAY ZEUS4D ♻️
-📌 Sharat Dan Ketentuan :
-🔸 Berlaku Untuk Bola Resmi Di Taruhan HDP Over Under 1x2 HT FT Sebelum Kick Off Provaider SBO CMD SABA.
-➡️ Stake 10K Min Odds 1.70 Boleh Lebih
-➡️ Stake 30 Min Odds 1.80 Boleh Lebih
-➡️ Min Stake 50 Min Odds 1.85 Boleh Lebih
-🔸Wajib Menggunakan Taruhan ¼ ¾ 1¼ 1¾ 2¼ 2¾ 3¼ Dan Seterusnya Minimal 3 Tim Ditaruhan HDP HT / FT
-🔸Tidak Ada Batasan Jumlah Bill Yang Akan Dishare Untuk Di Jadikan Taruhan.
-🔸 Bebas Untuk Kesamaan Tim Ditaruhan Yang Sama, Contoh Bill 1 Ambil Madrid Over 2.5 FT Maka Untuk Bill Yang Lainnya Jika Ingin Mengambil Tim Yang Sama Wajib Madrid Over 2.5 FT Lagi.
-❌ Tim Sama Beda Pasaran Dari Over Menjadi Under / Menjadi HDP / Menjadi 1x2 Maka Semua Bill Dinyatakan Hangus.
-LINK GROUP TELEGRAM : https://t.me /ZEUS4DOFFICIAL 
-LINK DAFTAR :  
- https://situsslotzeusstore/zeus4d</t>
-  </si>
-  <si>
-    <t>simbol daur ulang acara parlay zeusd simbol daur ulang paku tanda syarat wajik oranye laku bola resmi taruh hdp over under x ht ft kick off provider sbo cmd saba tanda panah kanan taruh k min odds tanda panah kanan taruh menit peluang tanda panah kanan min stake min odds wajik oranye taruh minimal tim taruh hdp ht ft wajik oranye batas uang taruh wajik oranye gratis taruh tim bill ambil madrid over ft bill ambil tim madrid ambil madrid over ft tanda silang tim pasar beda hdp x tagih nyata hangus link grup telegram {LINK} zeusdofficial link daftar {LINK}</t>
   </si>
 </sst>
 </file>
@@ -3893,7 +3821,7 @@
   <dimension ref="A1:B501"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="100.21875" customWidth="1"/>
+    <col min="1" max="1" width="90.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -4036,20 +3964,20 @@
       <c r="A18" t="s">
         <v>34</v>
       </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4169,2444 +4097,2447 @@
       <c r="A35" t="s">
         <v>67</v>
       </c>
+      <c r="B35" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B40" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B43" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B44" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B46" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B47" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B49" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B52" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B53" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B54" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B55" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B56" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B57" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B58" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B59" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B60" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B61" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B62" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B63" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B64" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B65" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B66" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B67" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B68" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B69" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B70" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B71" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B72" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B73" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B74" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B75" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B76" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B77" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B78" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B79" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B80" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B81" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B82" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B83" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B84" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B85" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B86" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B87" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B88" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>174</v>
+        <v>175</v>
+      </c>
+      <c r="B89" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B90" t="s">
-        <v>27</v>
+        <v>178</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B91" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B92" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B93" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>182</v>
-      </c>
-      <c r="B94" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B95" t="s">
-        <v>73</v>
+        <v>187</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B96" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B97" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B98" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B99" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B100" t="s">
-        <v>194</v>
+        <v>84</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B101" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B102" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B103" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B104" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B105" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B106" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B107" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B108" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B109" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B110" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B111" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B112" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B113" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B114" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B115" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B116" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B117" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B118" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B119" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B120" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B121" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B122" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B123" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B124" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B125" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B126" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B127" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B128" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B129" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B130" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B131" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B132" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B133" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B134" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B135" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B136" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B137" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B138" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B139" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B140" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B141" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B142" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B143" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B144" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B145" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B146" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B147" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B148" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B149" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B150" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B151" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B152" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B153" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B154" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B155" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B156" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B157" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B158" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B159" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B160" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B161" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B162" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B163" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B164" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B165" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B166" t="s">
-        <v>149</v>
+        <v>328</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B167" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B168" t="s">
-        <v>151</v>
+        <v>332</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B169" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B170" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B171" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B172" t="s">
-        <v>336</v>
+        <v>160</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B173" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B174" t="s">
-        <v>340</v>
+        <v>162</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B175" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B176" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B177" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B178" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B179" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B180" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B181" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B182" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B183" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B184" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B185" t="s">
-        <v>145</v>
+        <v>364</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B186" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B187" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B188" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B189" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B190" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B191" t="s">
-        <v>373</v>
+        <v>156</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B192" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B193" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B194" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B195" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B196" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B197" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B198" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B199" t="s">
-        <v>38</v>
+        <v>132</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>389</v>
+        <v>391</v>
+      </c>
+      <c r="B200" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B201" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B202" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B203" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B204" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B205" t="s">
-        <v>399</v>
+        <v>44</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>400</v>
-      </c>
-      <c r="B206" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B207" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B208" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B209" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B210" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B211" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B212" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B213" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B214" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B215" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B216" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B217" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B218" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B219" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B220" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B221" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B222" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B223" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B224" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B225" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B226" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B227" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B228" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B229" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B230" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B231" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B232" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B233" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B234" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B235" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B236" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B237" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B238" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B239" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B240" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B241" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B242" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B243" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B244" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B245" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B246" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B247" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B248" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B249" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B250" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B251" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B252" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B253" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B254" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B255" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B256" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B257" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B258" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B259" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B260" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B261" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B262" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B263" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B264" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B265" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B266" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B267" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B268" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B269" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B270" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>530</v>
+        <v>531</v>
+      </c>
+      <c r="B271" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B272" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B273" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B274" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B275" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B276" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B277" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B278" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B279" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B280" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B281" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B282" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B283" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B284" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B285" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B286" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B287" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B288" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B289" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>567</v>
-      </c>
-      <c r="B290" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B291" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B292" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B293" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B294" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B295" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B296" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B297" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B298" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B299" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B300" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B301" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B302" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B303" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B304" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B305" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B306" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B307" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B308" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B309" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B310" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B311" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B312" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B313" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B314" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B315" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B316" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B317" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B318" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B319" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B320" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B321" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B322" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B323" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B324" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B325" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B326" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B327" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B328" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B329" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B330" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B331" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B332" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B333" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B334" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B335" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B336" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B337" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B338" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B339" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B340" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B341" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.3">
@@ -7054,751 +6985,751 @@
         <v>781</v>
       </c>
       <c r="B397" t="s">
-        <v>395</v>
+        <v>782</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B398" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B399" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B400" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B401" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B402" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B403" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B404" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B405" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B406" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B407" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B408" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B409" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B410" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B411" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B412" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B413" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B414" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B415" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B416" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B417" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B418" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B419" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B420" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B421" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B422" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B423" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B424" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B425" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B426" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B427" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B428" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B429" t="s">
-        <v>145</v>
+        <v>846</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B430" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B431" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B432" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B433" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B434" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B435" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B436" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B437" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B438" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B439" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="B440" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B441" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B442" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B443" t="s">
-        <v>872</v>
+        <v>408</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B444" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B445" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B446" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B447" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B448" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B449" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B450" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B451" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B452" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B453" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B454" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B455" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B456" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B457" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B458" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B459" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B460" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B461" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B462" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B463" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B464" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B465" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B466" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B467" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B468" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B469" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B470" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B471" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B472" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B473" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B474" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B475" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B476" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B477" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B478" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B479" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B480" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B481" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B482" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B483" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B484" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B485" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B486" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B487" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B488" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B489" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B490" t="s">
-        <v>965</v>
+        <v>156</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.3">
@@ -7830,63 +7761,63 @@
         <v>972</v>
       </c>
       <c r="B494" t="s">
-        <v>973</v>
+        <v>877</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
+        <v>973</v>
+      </c>
+      <c r="B495" t="s">
         <v>974</v>
-      </c>
-      <c r="B495" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
+        <v>975</v>
+      </c>
+      <c r="B496" t="s">
         <v>976</v>
-      </c>
-      <c r="B496" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
+        <v>977</v>
+      </c>
+      <c r="B497" t="s">
         <v>978</v>
-      </c>
-      <c r="B497" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
+        <v>979</v>
+      </c>
+      <c r="B498" t="s">
         <v>980</v>
-      </c>
-      <c r="B498" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
+        <v>981</v>
+      </c>
+      <c r="B499" t="s">
         <v>982</v>
-      </c>
-      <c r="B499" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
+        <v>983</v>
+      </c>
+      <c r="B500" t="s">
         <v>984</v>
-      </c>
-      <c r="B500" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
+        <v>985</v>
+      </c>
+      <c r="B501" t="s">
         <v>986</v>
-      </c>
-      <c r="B501" t="s">
-        <v>987</v>
       </c>
     </row>
   </sheetData>
